--- a/📊 Websites_Master_List.xlsx
+++ b/📊 Websites_Master_List.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Websites Master" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music  Audio Streaming" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global TV  Media Discovery" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Video  Media Downloaders" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI  Machine Learning Tools" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Free Courses  Learning Platfo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PDF  Document Utilities" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web Utilities  Productivity" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design  Creator Tools" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gaming  Entertainment" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Online Radio  Interactive Map" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global TV  Media Discovery" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Video  Media Downloaders" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI  Machine Learning Tools" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Free Courses  Learning Platfo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PDF  Document Utilities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web Utilities  Productivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design  Creator Tools" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gaming  Entertainment" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,22 +894,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fame Lack</t>
+          <t>Radio Garden</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Global TV Discovery</t>
+          <t>Online Radio Map</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>📺 Global TV &amp; Media Discovery</t>
+          <t>📻 Online Radio &amp; Interactive Maps</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>https://famelack.com</t>
+          <t>https://radio.garden</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -918,7 +919,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Watch free live TV streams, international webcams, and explore worldwide broadcasting channels.</t>
+          <t>Interactive 3D globe allowing users to rotate the earth and tune into live radio stations worldwide.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -933,7 +934,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>TV Garden</t>
+          <t>Fame Lack</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -948,7 +949,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://tv.garden</t>
+          <t>https://famelack.com</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -958,7 +959,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Global television discovery platform to watch live broadcasts and international channels.</t>
+          <t>Watch free live TV streams, international webcams, and explore worldwide broadcasting channels.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -973,12 +974,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ZoomQuilt</t>
+          <t>TV Garden</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Interactive Visual Experience</t>
+          <t>Global TV Discovery</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -988,7 +989,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>https://zoomquilt.org</t>
+          <t>https://tv.garden</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -998,12 +999,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Interactive Visual Experience</t>
+          <t>Global television discovery platform to watch live broadcasts and international channels.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>User Chat Prompt</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1014,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>EarthCam</t>
+          <t>ZoomQuilt</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Live Camera Streaming</t>
+          <t>Interactive Visual Experience</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1028,7 +1029,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.earthcam.com</t>
+          <t>https://zoomquilt.org</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1038,7 +1039,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Live Camera Streaming</t>
+          <t>High-utility web tool: Interactive Visual Experience</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1053,12 +1054,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>90s.myretrotvs.com</t>
+          <t>EarthCam</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Retro TV Channel Simulator</t>
+          <t>Live Camera Streaming</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>https://90s.myretrotvs.com</t>
+          <t>https://www.earthcam.com</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1078,12 +1079,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Nostalgic 90s TV channel experience that recreates the feeling of old-school channel surfing</t>
+          <t>High-utility web tool: Live Camera Streaming</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1094,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Virtual Vacation</t>
+          <t>90s.myretrotvs.com</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Virtual Travel</t>
+          <t>Retro TV Channel Simulator</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1108,7 +1109,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://virtualvacation.us</t>
+          <t>https://90s.myretrotvs.com</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1118,12 +1119,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Virtual Travel</t>
+          <t>Nostalgic 90s TV channel experience that recreates the feeling of old-school channel surfing</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -1133,22 +1134,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Faceb.com (Facebook URL Trick)</t>
+          <t>Virtual Vacation</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Facebook Video Direct Downloader (URL Trick)</t>
+          <t>Virtual Travel</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>⬇️ Video &amp; Media Downloaders</t>
+          <t>📺 Global TV &amp; Media Discovery</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>https://www.faceb.com</t>
+          <t>https://virtualvacation.us</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1158,12 +1159,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Directly download Facebook videos by removing 'ook' from facebook.com in the browser URL.</t>
+          <t>High-utility web tool: Virtual Travel</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1174,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>BotDownloader (Facebook)</t>
+          <t>Faceb.com (Facebook URL Trick)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Facebook Video Downloader</t>
+          <t>Facebook Video Direct Downloader (URL Trick)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1188,7 +1189,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://botdownloader.com/facebook-video-downloader</t>
+          <t>https://www.faceb.com</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1198,12 +1199,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Facebook Video Downloader</t>
+          <t>Directly download Facebook videos by removing 'ook' from facebook.com in the browser URL.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 3)</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1214,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>FDown</t>
+          <t>BotDownloader (Facebook)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1228,7 +1229,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>https://fdown.net/download.php</t>
+          <t>https://botdownloader.com/facebook-video-downloader</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1253,12 +1254,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>iGram</t>
+          <t>FDown</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Instagram Downloader</t>
+          <t>Facebook Video Downloader</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1268,7 +1269,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://igram.io/en/dl</t>
+          <t>https://fdown.net/download.php</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1278,7 +1279,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Instagram Downloader</t>
+          <t>High-speed online tool: Facebook Video Downloader</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1293,12 +1294,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Instag.com (Instagram URL Trick)</t>
+          <t>iGram</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Instagram HD Reel Direct Downloader (URL Trick)</t>
+          <t>Instagram Downloader</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1308,7 +1309,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>https://www.instag.com</t>
+          <t>https://igram.io/en/dl</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1318,12 +1319,12 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Directly download Instagram Reels in highest available quality by removing 'ram' from instagram.com in the browser URL.</t>
+          <t>High-speed online tool: Instagram Downloader</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 2)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>BotDownloader (Pinterest)</t>
+          <t>Instag.com (Instagram URL Trick)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Pinterest Video Downloader</t>
+          <t>Instagram HD Reel Direct Downloader (URL Trick)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1348,7 +1349,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://botdownloader.com/pinterest-video-downloader</t>
+          <t>https://www.instag.com</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1358,12 +1359,12 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Pinterest Video Downloader</t>
+          <t>Directly download Instagram Reels in highest available quality by removing 'ram' from instagram.com in the browser URL.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 2)</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1374,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>AutoSubtitles (GitHub)</t>
+          <t>BotDownloader (Pinterest)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Subtitle Automation Tool</t>
+          <t>Pinterest Video Downloader</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1388,7 +1389,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/aman2k4/StartupBaniya/tree/main/autosubtitles</t>
+          <t>https://botdownloader.com/pinterest-video-downloader</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1398,7 +1399,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Subtitle Automation Tool</t>
+          <t>High-speed online tool: Pinterest Video Downloader</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1413,12 +1414,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>BotDownloader (Twitter)</t>
+          <t>AutoSubtitles (GitHub)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Twitter Video Downloader</t>
+          <t>Subtitle Automation Tool</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1428,7 +1429,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://botdownloader.com/twitter-video-downloader</t>
+          <t>https://github.com/aman2k4/StartupBaniya/tree/main/autosubtitles</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1438,7 +1439,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Twitter Video Downloader</t>
+          <t>High-speed online tool: Subtitle Automation Tool</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1453,12 +1454,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cobalt Tools</t>
+          <t>BotDownloader (Twitter)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Universal Media Downloader</t>
+          <t>Twitter Video Downloader</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1468,7 +1469,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>https://cobalt.tools</t>
+          <t>https://botdownloader.com/twitter-video-downloader</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1478,7 +1479,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Universal Media Downloader</t>
+          <t>High-speed online tool: Twitter Video Downloader</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1493,12 +1494,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Y2Mate</t>
+          <t>Cobalt Tools</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>YouTube to MP4 Converter</t>
+          <t>Universal Media Downloader</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1508,7 +1509,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://y2mate.lol/en98/youtube-to-mp4</t>
+          <t>https://cobalt.tools</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1518,7 +1519,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube to MP4 Converter</t>
+          <t>High-speed online tool: Universal Media Downloader</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1533,12 +1534,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Yout.com (YouTube URL Trick)</t>
+          <t>Y2Mate</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>YouTube Video &amp; MP3 Downloader (URL Trick)</t>
+          <t>YouTube to MP4 Converter</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1548,7 +1549,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>https://www.yout.com</t>
+          <t>https://y2mate.lol/en98/youtube-to-mp4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1558,12 +1559,12 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Directly download any YouTube video as MP4 or MP3 by removing 'ube' from youtube.com in the browser URL.</t>
+          <t>High-speed online tool: YouTube to MP4 Converter</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 1)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1574,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>YouTube Video &amp; MP3 Timestamp Downloader (Instagram Reel Guide)</t>
+          <t>Yout.com (YouTube URL Trick)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>YouTube Video , Mp3 download with timestamp</t>
+          <t>YouTube Video &amp; MP3 Downloader (URL Trick)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1588,7 +1589,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DcyyG0Tvhqb/?stkn=MXJ6c2dmdmtteGJpaA==</t>
+          <t>https://www.yout.com</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1598,12 +1599,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube Video , Mp3 download with timestamp</t>
+          <t>Directly download any YouTube video as MP4 or MP3 by removing 'ube' from youtube.com in the browser URL.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 1)</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1614,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>SSYouTube</t>
+          <t>YouTube Video &amp; MP3 Timestamp Downloader (Instagram Reel Guide)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>YouTube Video Downloader</t>
+          <t>YouTube Video , Mp3 download with timestamp</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1628,7 +1629,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>https://ssyoutube.com/en1/youtube-video-downloader</t>
+          <t>https://www.instagram.com/reel/DcyyG0Tvhqb/?stkn=MXJ6c2dmdmtteGJpaA==</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1638,7 +1639,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube Video Downloader</t>
+          <t>High-speed online tool: YouTube Video , Mp3 download with timestamp</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1653,37 +1654,37 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>heyzxz.me</t>
+          <t>SSYouTube</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>AI Audio &amp; Voice Tool</t>
+          <t>YouTube Video Downloader</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
+          <t>⬇️ Video &amp; Media Downloaders</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://heyzxz.me</t>
+          <t>https://ssyoutube.com/en1/youtube-video-downloader</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>AI voice synthesis and cloning for content creators needing voiceovers without recording</t>
+          <t>High-speed online tool: YouTube Video Downloader</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1694,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>freepik.com</t>
+          <t>heyzxz.me</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>AI Image Generator &amp; Enhancer</t>
+          <t>AI Audio &amp; Voice Tool</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1708,7 +1709,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>https://freepik.com</t>
+          <t>https://heyzxz.me</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1718,7 +1719,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Stock graphics library with AI image generation tools - one-stop shop for visual assets</t>
+          <t>AI voice synthesis and cloning for content creators needing voiceovers without recording</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1733,7 +1734,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>meshy.ai</t>
+          <t>freepik.com</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1748,7 +1749,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://meshy.ai</t>
+          <t>https://freepik.com</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1758,7 +1759,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>AI generates 3D models from text prompts or images for games and visualization</t>
+          <t>Stock graphics library with AI image generation tools - one-stop shop for visual assets</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1773,7 +1774,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>newarc.ai</t>
+          <t>meshy.ai</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1788,7 +1789,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>https://newarc.ai</t>
+          <t>https://meshy.ai</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1798,7 +1799,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>AI architecture design tool that generates photorealistic building visualizations from concepts</t>
+          <t>AI generates 3D models from text prompts or images for games and visualization</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1813,7 +1814,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>reimaginehome.ai</t>
+          <t>newarc.ai</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1828,7 +1829,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://reimaginehome.ai</t>
+          <t>https://newarc.ai</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1838,7 +1839,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Upload a room photo and get AI-generated interior design ideas in different styles</t>
+          <t>AI architecture design tool that generates photorealistic building visualizations from concepts</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -1853,7 +1854,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>remove.photos</t>
+          <t>reimaginehome.ai</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1868,7 +1869,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>https://remove.photos</t>
+          <t>https://reimaginehome.ai</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1878,7 +1879,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>AI background remover for quick photo editing in your browser - no software needed</t>
+          <t>Upload a room photo and get AI-generated interior design ideas in different styles</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -1893,12 +1894,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>autodraw.com</t>
+          <t>remove.photos</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>AI Productivity &amp; Generation Tool</t>
+          <t>AI Image Generator &amp; Enhancer</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1908,17 +1909,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://autodraw.com</t>
+          <t>https://remove.photos</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Google's AI that turns rough sketches into clean professional drawings instantly</t>
+          <t>AI background remover for quick photo editing in your browser - no software needed</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -1933,7 +1934,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>chef.convex.dev</t>
+          <t>autodraw.com</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1948,17 +1949,17 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>https://chef.convex.dev</t>
+          <t>https://autodraw.com</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>AI generates real-time app backends from prompts - deploy working prototypes in minutes</t>
+          <t>Google's AI that turns rough sketches into clean professional drawings instantly</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -1973,7 +1974,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>chefgpt.xyz</t>
+          <t>chef.convex.dev</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1988,17 +1989,17 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://chefgpt.xyz</t>
+          <t>https://chef.convex.dev</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>AI suggests recipes based on ingredients already in your fridge to reduce food waste</t>
+          <t>AI generates real-time app backends from prompts - deploy working prototypes in minutes</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2013,7 +2014,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>collov.ai</t>
+          <t>chefgpt.xyz</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2028,17 +2029,17 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>https://collov.ai</t>
+          <t>https://chefgpt.xyz</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>AI virtual home staging that transforms empty rooms into furnished spaces for listings</t>
+          <t>AI suggests recipes based on ingredients already in your fridge to reduce food waste</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2053,7 +2054,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>coze.com</t>
+          <t>collov.ai</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2068,7 +2069,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://coze.com</t>
+          <t>https://collov.ai</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2078,7 +2079,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Build custom AI chatbots and agents without code - deploy to messaging platforms</t>
+          <t>AI virtual home staging that transforms empty rooms into furnished spaces for listings</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2093,7 +2094,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>flowith.io</t>
+          <t>coze.com</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2108,7 +2109,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>https://flowith.io</t>
+          <t>https://coze.com</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2118,7 +2119,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>AI workspace with infinite canvas for non-linear conversations and complex reasoning tasks</t>
+          <t>Build custom AI chatbots and agents without code - deploy to messaging platforms</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2133,7 +2134,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>gptexcel.uk</t>
+          <t>flowith.io</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2148,7 +2149,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://gptexcel.uk</t>
+          <t>https://flowith.io</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2158,7 +2159,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>AI generates spreadsheet formulas from plain English - stop memorizing VLOOKUP syntax</t>
+          <t>AI workspace with infinite canvas for non-linear conversations and complex reasoning tasks</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2173,7 +2174,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>kittl.com</t>
+          <t>gptexcel.uk</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2188,7 +2189,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>https://kittl.com</t>
+          <t>https://gptexcel.uk</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2198,7 +2199,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>AI-powered design tool perfect for print-on-demand sellers creating professional graphics quickly</t>
+          <t>AI generates spreadsheet formulas from plain English - stop memorizing VLOOKUP syntax</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2213,7 +2214,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>layla.ai</t>
+          <t>kittl.com</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2228,7 +2229,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://layla.ai</t>
+          <t>https://kittl.com</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2238,7 +2239,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>AI travel itinerary planner that creates balanced trip plans from your preferences</t>
+          <t>AI-powered design tool perfect for print-on-demand sellers creating professional graphics quickly</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2253,7 +2254,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>natively.dev</t>
+          <t>layla.ai</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2268,7 +2269,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>https://natively.dev</t>
+          <t>https://layla.ai</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2278,7 +2279,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>AI no-code platform for building native mobile apps without any programming knowledge</t>
+          <t>AI travel itinerary planner that creates balanced trip plans from your preferences</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2293,7 +2294,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>same.new</t>
+          <t>natively.dev</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2308,7 +2309,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://same.new</t>
+          <t>https://natively.dev</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2318,7 +2319,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>AI clones any website's design in seconds and generates the code for you</t>
+          <t>AI no-code platform for building native mobile apps without any programming knowledge</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2333,7 +2334,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>sketch.metademolab.com</t>
+          <t>same.new</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2348,17 +2349,17 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>https://sketch.metademolab.com</t>
+          <t>https://same.new</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Meta's AI that automatically animates hand-drawn character sketches - free research demo</t>
+          <t>AI clones any website's design in seconds and generates the code for you</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2373,12 +2374,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>intangible.ai</t>
+          <t>sketch.metademolab.com</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>AI Video Generation &amp; Pre-Production</t>
+          <t>AI Productivity &amp; Generation Tool</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2388,17 +2389,17 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://intangible.ai</t>
+          <t>https://sketch.metademolab.com</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>AI video generation for pre-production visualization - save thousands on production costs</t>
+          <t>Meta's AI that automatically animates hand-drawn character sketches - free research demo</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2413,12 +2414,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>replit.com</t>
+          <t>intangible.ai</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>AI Website Builder &amp; IDE</t>
+          <t>AI Video Generation &amp; Pre-Production</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2428,7 +2429,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>https://replit.com</t>
+          <t>https://intangible.ai</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2438,7 +2439,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Fastest and most accurate AI website builder I've tried so far.</t>
+          <t>AI video generation for pre-production visualization - save thousands on production costs</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2453,12 +2454,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>app.emergent.sh</t>
+          <t>replit.com</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>AI Writing &amp; Copywriting Assistant</t>
+          <t>AI Website Builder &amp; IDE</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2468,7 +2469,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://app.emergent.sh</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2478,7 +2479,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>AI builds functional web app MVPs from text prompts - great for rapid prototyping</t>
+          <t>Fastest and most accurate AI website builder I've tried so far.</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2493,7 +2494,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>enzostvs-deepsite.hf.space</t>
+          <t>app.emergent.sh</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2508,17 +2509,17 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>https://enzostvs-deepsite.hf.space</t>
+          <t>https://app.emergent.sh</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>AI generates complete websites from text prompts using open-source models - free hosting included</t>
+          <t>AI builds functional web app MVPs from text prompts - great for rapid prototyping</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2533,7 +2534,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>gamma.app</t>
+          <t>enzostvs-deepsite.hf.space</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2548,17 +2549,17 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://gamma.app</t>
+          <t>https://enzostvs-deepsite.hf.space</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>AI generates complete presentations from text - turn ideas into slides in minutes</t>
+          <t>AI generates complete websites from text prompts using open-source models - free hosting included</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -2573,7 +2574,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>napkin.ai</t>
+          <t>gamma.app</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2588,7 +2589,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>https://napkin.ai</t>
+          <t>https://gamma.app</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2598,7 +2599,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>AI transforms text into visual diagrams and illustrations automatically - just paste and go</t>
+          <t>AI generates complete presentations from text - turn ideas into slides in minutes</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2613,7 +2614,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>ponder.chat</t>
+          <t>napkin.ai</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2628,7 +2629,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://ponder.chat</t>
+          <t>https://napkin.ai</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2638,7 +2639,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>AI writing assistant for creating blog posts social media content and marketing copy</t>
+          <t>AI transforms text into visual diagrams and illustrations automatically - just paste and go</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2653,7 +2654,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>text-to-cad.zoo.dev</t>
+          <t>ponder.chat</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2668,17 +2669,17 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>https://text-to-cad.zoo.dev</t>
+          <t>https://ponder.chat</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>AI generates 3D CAD models from text descriptions for engineering and design projects</t>
+          <t>AI writing assistant for creating blog posts social media content and marketing copy</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2693,22 +2694,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>A B C of Coding to Build AI Agents</t>
+          <t>text-to-cad.zoo.dev</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Agentic AI Course</t>
+          <t>AI Writing &amp; Copywriting Assistant</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>🎓 Free Courses &amp; Learning Platforms</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/a-b-c-of-coding-to-build-ai-agents</t>
+          <t>https://text-to-cad.zoo.dev</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2718,12 +2719,12 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: A B C of Coding to Build AI Agents (Agentic AI Course)</t>
+          <t>AI generates 3D CAD models from text descriptions for engineering and design projects</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2734,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Agentic : AI Design Pattern</t>
+          <t>A B C of Coding to Build AI Agents</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2748,7 +2749,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/agentic-ai-design-pattern</t>
+          <t>https://www.analyticsvidhya.com/courses/a-b-c-of-coding-to-build-ai-agents</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2758,7 +2759,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Agentic : AI Design Pattern (Agentic AI Course)</t>
+          <t>Comprehensive free training course: A B C of Coding to Build AI Agents (Agentic AI Course)</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -2773,7 +2774,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Build a Resume Review Agentic System with CrewAI</t>
+          <t>Agentic : AI Design Pattern</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2788,7 +2789,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/build-a-resume-review-agentic-system-with-crewai</t>
+          <t>https://www.analyticsvidhya.com/courses/agentic-ai-design-pattern</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2798,7 +2799,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Build a Resume Review Agentic System with CrewAI (Agentic AI Course)</t>
+          <t>Comprehensive free training course: Agentic : AI Design Pattern (Agentic AI Course)</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -2813,7 +2814,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Building Agentic AI System with Bedrock</t>
+          <t>Build a Resume Review Agentic System with CrewAI</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2828,7 +2829,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/building-agentic-ai-system-with-with-bedrock</t>
+          <t>https://www.analyticsvidhya.com/courses/build-a-resume-review-agentic-system-with-crewai</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2838,7 +2839,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Building Agentic AI System with Bedrock (Agentic AI Course)</t>
+          <t>Comprehensive free training course: Build a Resume Review Agentic System with CrewAI (Agentic AI Course)</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -2853,7 +2854,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Knowledge Bases &amp; Memory for Agentic AI</t>
+          <t>Building Agentic AI System with Bedrock</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2868,7 +2869,7 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/knowledge-bases-and-memory-for-agentic-ai</t>
+          <t>https://www.analyticsvidhya.com/courses/building-agentic-ai-system-with-with-bedrock</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2878,7 +2879,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Knowledge Bases &amp; Memory for Agentic AI (Agentic AI Course)</t>
+          <t>Comprehensive free training course: Building Agentic AI System with Bedrock (Agentic AI Course)</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -2893,12 +2894,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Elements of AI</t>
+          <t>Knowledge Bases &amp; Memory for Agentic AI</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>AI Course Platform</t>
+          <t>Agentic AI Course</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2908,7 +2909,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>https://www.elementsofai.com</t>
+          <t>https://www.analyticsvidhya.com/courses/knowledge-bases-and-memory-for-agentic-ai</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2918,12 +2919,12 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Elements of AI (AI Course Platform)</t>
+          <t>Comprehensive free training course: Knowledge Bases &amp; Memory for Agentic AI (Agentic AI Course)</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2934,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Deep Dive Into QwQ-32B</t>
+          <t>Elements of AI</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>AI Model Deep Dive Course</t>
+          <t>AI Course Platform</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2948,7 +2949,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/deep-dive-into-qwq-32b</t>
+          <t>https://www.elementsofai.com</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2958,12 +2959,12 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Deep Dive Into QwQ-32B (AI Model Deep Dive Course)</t>
+          <t>Free education and certified training: Elements of AI (AI Course Platform)</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2974,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Exploring OpenAI o3 and o4-mini</t>
+          <t>Deep Dive Into QwQ-32B</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2988,7 +2989,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/exploring-openai-o3-and-o4-mini</t>
+          <t>https://www.analyticsvidhya.com/courses/deep-dive-into-qwq-32b</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2998,7 +2999,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Exploring OpenAI o3 and o4-mini (AI Model Deep Dive Course)</t>
+          <t>Comprehensive free training course: Deep Dive Into QwQ-32B (AI Model Deep Dive Course)</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3013,7 +3014,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with DeepSeek-AI</t>
+          <t>Exploring OpenAI o3 and o4-mini</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3028,7 +3029,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/getting-started-with-deepseek</t>
+          <t>https://www.analyticsvidhya.com/courses/exploring-openai-o3-and-o4-mini</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3038,7 +3039,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Getting Started with DeepSeek-AI (AI Model Deep Dive Course)</t>
+          <t>Comprehensive free training course: Exploring OpenAI o3 and o4-mini (AI Model Deep Dive Course)</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3053,7 +3054,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with OpenAI o3-mini</t>
+          <t>Getting Started with DeepSeek-AI</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3068,7 +3069,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/getting-started-with-openai-o3-mini</t>
+          <t>https://www.analyticsvidhya.com/courses/getting-started-with-deepseek</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3078,7 +3079,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Getting Started with OpenAI o3-mini (AI Model Deep Dive Course)</t>
+          <t>Comprehensive free training course: Getting Started with DeepSeek-AI (AI Model Deep Dive Course)</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3093,7 +3094,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>xAI Grok 3: Smartest AI on Earth</t>
+          <t>Getting Started with OpenAI o3-mini</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3108,7 +3109,7 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/xai-grok-3-smartest-ai-on-earth</t>
+          <t>https://www.analyticsvidhya.com/courses/getting-started-with-openai-o3-mini</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3118,7 +3119,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: xAI Grok 3: Smartest AI on Earth (AI Model Deep Dive Course)</t>
+          <t>Comprehensive free training course: Getting Started with OpenAI o3-mini (AI Model Deep Dive Course)</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3133,12 +3134,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Databricks – Generative AI Fundamentals</t>
+          <t>xAI Grok 3: Smartest AI on Earth</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>AI Training Course</t>
+          <t>AI Model Deep Dive Course</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3148,7 +3149,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/learn/training/generative-ai-fundamentals</t>
+          <t>https://www.analyticsvidhya.com/courses/xai-grok-3-smartest-ai-on-earth</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3158,12 +3159,12 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Databricks – Generative AI Fundamentals (AI Training Course)</t>
+          <t>Comprehensive free training course: xAI Grok 3: Smartest AI on Earth (AI Model Deep Dive Course)</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3174,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Google Cloud Skills Boost</t>
+          <t>Databricks – Generative AI Fundamentals</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Cloud Training Path</t>
+          <t>AI Training Course</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3188,22 +3189,22 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.cloudskillsboost.google/paths/118</t>
+          <t>https://www.databricks.com/learn/training/generative-ai-fundamentals</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Google Cloud Skills Boost (Cloud Training Path)</t>
+          <t>Free education and certified training: Databricks – Generative AI Fundamentals (AI Training Course)</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Google)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3214,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>STP Computer Education – Courses</t>
+          <t>Google Cloud Skills Boost</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Computer Courses Platform</t>
+          <t>Cloud Training Path</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3228,7 +3229,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>https://www.stpcomputereducation.com/courses</t>
+          <t>https://www.cloudskillsboost.google/paths/118</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3238,12 +3239,12 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: STP Computer Education – Courses (Computer Courses Platform)</t>
+          <t>Free education and certified training: Google Cloud Skills Boost (Cloud Training Path)</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Computer)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Google)</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3254,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>chemequations.com</t>
+          <t>STP Computer Education – Courses</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Educational Learning Platform</t>
+          <t>Computer Courses Platform</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3268,22 +3269,22 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://chemequations.com</t>
+          <t>https://www.stpcomputereducation.com/courses</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Auto-balance chemical equations instantly - essential tool for chemistry homework and learning</t>
+          <t>Free education and certified training: STP Computer Education – Courses (Computer Courses Platform)</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Computer)</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3294,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>classcentral.com</t>
+          <t>chemequations.com</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3308,7 +3309,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>https://classcentral.com</t>
+          <t>https://chemequations.com</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3318,7 +3319,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Search engine aggregating online courses from all major platforms with reviews and ratings</t>
+          <t>Auto-balance chemical equations instantly - essential tool for chemistry homework and learning</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3333,7 +3334,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>cymath.com</t>
+          <t>classcentral.com</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3348,17 +3349,17 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://cymath.com</t>
+          <t>https://classcentral.com</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Step-by-step math problem solver that shows you how to get the answer</t>
+          <t>Search engine aggregating online courses from all major platforms with reviews and ratings</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -3373,7 +3374,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>dungeonscrawl.com</t>
+          <t>cymath.com</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3388,7 +3389,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>https://dungeonscrawl.com</t>
+          <t>https://cymath.com</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3398,7 +3399,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Create custom dungeon maps online for tabletop RPGs and virtual tabletop sessions</t>
+          <t>Step-by-step math problem solver that shows you how to get the answer</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3413,7 +3414,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>human.biodigital.com</t>
+          <t>dungeonscrawl.com</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3428,17 +3429,17 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://human.biodigital.com</t>
+          <t>https://dungeonscrawl.com</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Interactive 3D human anatomy model for medical students and curious minds to explore</t>
+          <t>Create custom dungeon maps online for tabletop RPGs and virtual tabletop sessions</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -3453,7 +3454,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>kiddoworksheets.com</t>
+          <t>human.biodigital.com</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3468,7 +3469,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>https://kiddoworksheets.com</t>
+          <t>https://human.biodigital.com</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3478,7 +3479,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Free printable worksheets for kids covering math reading and educational activities</t>
+          <t>Interactive 3D human anatomy model for medical students and curious minds to explore</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -3493,7 +3494,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>litsolutions.org</t>
+          <t>kiddoworksheets.com</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3508,7 +3509,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://litsolutions.org</t>
+          <t>https://kiddoworksheets.com</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3518,7 +3519,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Free textbook solutions and homework help with step-by-step workings for STEM courses</t>
+          <t>Free printable worksheets for kids covering math reading and educational activities</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -3533,7 +3534,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>mindluster.com</t>
+          <t>litsolutions.org</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3548,7 +3549,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>https://mindluster.com</t>
+          <t>https://litsolutions.org</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3558,7 +3559,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Free online courses with certificates you can add to your resume upon completion</t>
+          <t>Free textbook solutions and homework help with step-by-step workings for STEM courses</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -3573,7 +3574,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>musicca.com</t>
+          <t>mindluster.com</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3588,7 +3589,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://musicca.com</t>
+          <t>https://mindluster.com</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3598,7 +3599,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Interactive music theory lessons with virtual instruments and exercises to practice concepts</t>
+          <t>Free online courses with certificates you can add to your resume upon completion</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -3613,7 +3614,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>phet.colorado.edu</t>
+          <t>musicca.com</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3628,7 +3629,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>https://phet.colorado.edu</t>
+          <t>https://musicca.com</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3638,7 +3639,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Free interactive science simulations from University of Colorado for physics chemistry and biology</t>
+          <t>Interactive music theory lessons with virtual instruments and exercises to practice concepts</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -3653,7 +3654,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>smart.servier.com</t>
+          <t>phet.colorado.edu</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3668,7 +3669,7 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://smart.servier.com</t>
+          <t>https://phet.colorado.edu</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3678,7 +3679,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Free high-resolution medical and scientific images for anatomy biology and healthcare projects</t>
+          <t>Free interactive science simulations from University of Colorado for physics chemistry and biology</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -3693,7 +3694,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>spacetypegenerator.com</t>
+          <t>smart.servier.com</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3708,7 +3709,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>https://spacetypegenerator.com</t>
+          <t>https://smart.servier.com</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3718,7 +3719,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Animated typography effects generator for creating dynamic text for videos and social media</t>
+          <t>Free high-resolution medical and scientific images for anatomy biology and healthcare projects</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -3733,7 +3734,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>typelit.io</t>
+          <t>spacetypegenerator.com</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3748,17 +3749,17 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://typelit.io</t>
+          <t>https://spacetypegenerator.com</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Practice typing by retyping classic literature - combine skill development with reading great books</t>
+          <t>Animated typography effects generator for creating dynamic text for videos and social media</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -3773,7 +3774,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>typingclub.com</t>
+          <t>typelit.io</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3788,7 +3789,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>https://typingclub.com</t>
+          <t>https://typelit.io</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -3798,7 +3799,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Structured typing lessons for schools and individuals with gamified progress tracking</t>
+          <t>Practice typing by retyping classic literature - combine skill development with reading great books</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -3813,7 +3814,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>wolframalpha.com</t>
+          <t>typingclub.com</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -3828,7 +3829,7 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://wolframalpha.com</t>
+          <t>https://typingclub.com</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3838,7 +3839,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Computational knowledge engine that answers questions with computed data rather than web links</t>
+          <t>Structured typing lessons for schools and individuals with gamified progress tracking</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -3853,7 +3854,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>zty.pe</t>
+          <t>wolframalpha.com</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3868,17 +3869,17 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>https://zty.pe</t>
+          <t>https://wolframalpha.com</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Typing game where you shoot down enemy ships by typing words - fun skill practice</t>
+          <t>Computational knowledge engine that answers questions with computed data rather than web links</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -3893,12 +3894,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Instagram – Learn English With Shaba</t>
+          <t>zty.pe</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>English Learning Page</t>
+          <t>Educational Learning Platform</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -3908,7 +3909,7 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/learn_english_with_shaba</t>
+          <t>https://zty.pe</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3918,12 +3919,12 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Instagram – Learn English With Shaba (English Learning Page)</t>
+          <t>Typing game where you shoot down enemy ships by typing words - fun skill practice</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (English)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -3933,12 +3934,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>YouTube – ES4TpVsTkgc</t>
+          <t>Instagram – Learn English With Shaba</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>English Learning Video</t>
+          <t>English Learning Page</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -3948,7 +3949,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>https://youtu.be/ES4TpVsTkgc</t>
+          <t>https://www.instagram.com/learn_english_with_shaba</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -3958,7 +3959,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: YouTube – ES4TpVsTkgc (English Learning Video)</t>
+          <t>Free education and certified training: Instagram – Learn English With Shaba (English Learning Page)</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -3973,12 +3974,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Data Science Free Program - 9 Courses Combo</t>
+          <t>YouTube – dLKPBSov2F4</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Free Program Combo Bundle</t>
+          <t>English Learning Video</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -3988,7 +3989,7 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/learning-path/data-science-program</t>
+          <t>https://youtu.be/ES4TpVsTkgc</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -3998,12 +3999,12 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Data Science Free Program - 9 Courses Combo (Free Program Combo Bundle)</t>
+          <t>Free education and certified training: YouTube – dLKPBSov2F4 (English Learning Video)</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
+          <t>Excel: 🎓 Course Library.xlsx (English)</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4014,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>GenAI Free Program - 7 Courses Combo</t>
+          <t>Data Science Free Program - 9 Courses Combo</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4028,7 +4029,7 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/learning-path/generative-ai-program-free</t>
+          <t>https://www.analyticsvidhya.com/courses/learning-path/data-science-program</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4038,7 +4039,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: GenAI Free Program - 7 Courses Combo (Free Program Combo Bundle)</t>
+          <t>Comprehensive free training course: Data Science Free Program - 9 Courses Combo (Free Program Combo Bundle)</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4053,12 +4054,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Essential : SQL Skills for Data Beginners</t>
+          <t>GenAI Free Program - 7 Courses Combo</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Fundamental Tech Course</t>
+          <t>Free Program Combo Bundle</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4068,7 +4069,7 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/essential-sql-skills-for-data-beginners</t>
+          <t>https://www.analyticsvidhya.com/courses/learning-path/generative-ai-program-free</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4078,7 +4079,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Essential : SQL Skills for Data Beginners (Fundamental Tech Course)</t>
+          <t>Comprehensive free training course: GenAI Free Program - 7 Courses Combo (Free Program Combo Bundle)</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -4093,7 +4094,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Excel : From Beginner to Expert</t>
+          <t>Essential : SQL Skills for Data Beginners</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -4108,7 +4109,7 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/excel-from-beginner-to-expert</t>
+          <t>https://www.analyticsvidhya.com/courses/essential-sql-skills-for-data-beginners</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4118,7 +4119,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Excel : From Beginner to Expert (Fundamental Tech Course)</t>
+          <t>Comprehensive free training course: Essential : SQL Skills for Data Beginners (Fundamental Tech Course)</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -4133,7 +4134,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>GenAI for Everyone</t>
+          <t>Excel : From Beginner to Expert</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4148,7 +4149,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/genai-landscape</t>
+          <t>https://www.analyticsvidhya.com/courses/excel-from-beginner-to-expert</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4158,7 +4159,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: GenAI for Everyone (Fundamental Tech Course)</t>
+          <t>Comprehensive free training course: Excel : From Beginner to Expert (Fundamental Tech Course)</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -4173,7 +4174,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Tableau</t>
+          <t>GenAI for Everyone</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4188,7 +4189,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/getting-started-with-tableau</t>
+          <t>https://www.analyticsvidhya.com/courses/genai-landscape</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4198,7 +4199,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Getting Started with Tableau (Fundamental Tech Course)</t>
+          <t>Comprehensive free training course: GenAI for Everyone (Fundamental Tech Course)</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -4213,7 +4214,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Introduction to Python</t>
+          <t>Getting Started with Tableau</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4228,7 +4229,7 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/introduction-to-data-science</t>
+          <t>https://www.analyticsvidhya.com/courses/getting-started-with-tableau</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4238,7 +4239,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Introduction to Python (Fundamental Tech Course)</t>
+          <t>Comprehensive free training course: Getting Started with Tableau (Fundamental Tech Course)</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -4253,12 +4254,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Build Products 10x Faster with GenAI</t>
+          <t>Introduction to Python</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Generative AI Course</t>
+          <t>Fundamental Tech Course</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4268,7 +4269,7 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/build-product-10x-faster-with-genai</t>
+          <t>https://www.analyticsvidhya.com/courses/introduction-to-data-science</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4278,7 +4279,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Build Products 10x Faster with GenAI (Generative AI Course)</t>
+          <t>Comprehensive free training course: Introduction to Python (Fundamental Tech Course)</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -4293,7 +4294,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>DeepSeek from Scratch</t>
+          <t>Build Products 10x Faster with GenAI</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4308,7 +4309,7 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/deepseek-from-scratch</t>
+          <t>https://www.analyticsvidhya.com/courses/build-product-10x-faster-with-genai</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4318,7 +4319,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: DeepSeek from Scratch (Generative AI Course)</t>
+          <t>Comprehensive free training course: Build Products 10x Faster with GenAI (Generative AI Course)</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -4333,7 +4334,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>GenAI for Quantitative Finance &amp; Control Implementation</t>
+          <t>DeepSeek from Scratch</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4348,7 +4349,7 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/genai-applied-to-quantitative-finance-for-control-implementation</t>
+          <t>https://www.analyticsvidhya.com/courses/deepseek-from-scratch</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4358,7 +4359,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: GenAI for Quantitative Finance &amp; Control Implementation (Generative AI Course)</t>
+          <t>Comprehensive free training course: DeepSeek from Scratch (Generative AI Course)</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -4373,7 +4374,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Generative AI - A Way of Life</t>
+          <t>GenAI for Quantitative Finance &amp; Control Implementation</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -4388,7 +4389,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/genai-a-way-of-life</t>
+          <t>https://www.analyticsvidhya.com/courses/genai-applied-to-quantitative-finance-for-control-implementation</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4398,7 +4399,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Generative AI - A Way of Life (Generative AI Course)</t>
+          <t>Comprehensive free training course: GenAI for Quantitative Finance &amp; Control Implementation (Generative AI Course)</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -4413,7 +4414,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Reimagining GenAI: Common Mistakes and Best Practices for Success</t>
+          <t>Generative AI - A Way of Life</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4428,7 +4429,7 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/reimagining-genai-common-mistakes-and-best-practices-for-success</t>
+          <t>https://www.analyticsvidhya.com/courses/genai-a-way-of-life</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4438,7 +4439,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Reimagining GenAI: Common Mistakes and Best Practices for Success (Generative AI Course)</t>
+          <t>Comprehensive free training course: Generative AI - A Way of Life (Generative AI Course)</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -4453,12 +4454,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>A Complete MLops Journey</t>
+          <t>Reimagining GenAI: Common Mistakes and Best Practices for Success</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Deep Learning Course</t>
+          <t>Generative AI Course</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -4468,7 +4469,7 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/a-complete-mlops-journey</t>
+          <t>https://www.analyticsvidhya.com/courses/reimagining-genai-common-mistakes-and-best-practices-for-success</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4478,7 +4479,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: A Complete MLops Journey (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Reimagining GenAI: Common Mistakes and Best Practices for Success (Generative AI Course)</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -4493,7 +4494,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>A Comprehensive Learning Path to Become a Data Scientist in 2025</t>
+          <t>A Complete MLops Journey</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4508,7 +4509,7 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/a-comprehensive-learning-path-to-become-a-data-scientist-in-twenty-twenty-four</t>
+          <t>https://www.analyticsvidhya.com/courses/a-complete-mlops-journey</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4518,7 +4519,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: A Comprehensive Learning Path to Become a Data Scientist in 2025 (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: A Complete MLops Journey (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -4533,7 +4534,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Bagging and Boosting ML Algorithms</t>
+          <t>A Comprehensive Learning Path to Become a Data Scientist in 2025</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4548,7 +4549,7 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/bagging-boosting-ML-Algorithms</t>
+          <t>https://www.analyticsvidhya.com/courses/a-comprehensive-learning-path-to-become-a-data-scientist-in-twenty-twenty-four</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4558,7 +4559,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Bagging and Boosting ML Algorithms (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: A Comprehensive Learning Path to Become a Data Scientist in 2025 (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -4573,7 +4574,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Building Text Classification Models in NLP</t>
+          <t>Bagging and Boosting ML Algorithms</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4588,7 +4589,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/free-building-textclassification-natural-language-processing</t>
+          <t>https://www.analyticsvidhya.com/courses/bagging-boosting-ML-Algorithms</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -4598,7 +4599,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Building Text Classification Models in NLP (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Bagging and Boosting ML Algorithms (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -4613,7 +4614,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction for Machine Learning</t>
+          <t>Building Text Classification Models in NLP</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -4628,7 +4629,7 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/dimensionality-reduction-for-machine-learning</t>
+          <t>https://www.analyticsvidhya.com/courses/free-building-textclassification-natural-language-processing</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -4638,7 +4639,7 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Dimensionality Reduction for Machine Learning (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Building Text Classification Models in NLP (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -4653,7 +4654,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Ensemble Learning and Ensemble Learning Techniques</t>
+          <t>Dimensionality Reduction for Machine Learning</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4668,7 +4669,7 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/ensemble-learning-and-ensemble-learning-techniques</t>
+          <t>https://www.analyticsvidhya.com/courses/dimensionality-reduction-for-machine-learning</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -4678,7 +4679,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Ensemble Learning and Ensemble Learning Techniques (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Dimensionality Reduction for Machine Learning (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -4693,7 +4694,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Fundamentals of Regression Analysis</t>
+          <t>Ensemble Learning and Ensemble Learning Techniques</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4708,7 +4709,7 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/Fundamentals-of-Regression-Analysis</t>
+          <t>https://www.analyticsvidhya.com/courses/ensemble-learning-and-ensemble-learning-techniques</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -4718,7 +4719,7 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Fundamentals of Regression Analysis (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Ensemble Learning and Ensemble Learning Techniques (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -4733,7 +4734,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Deep Learning</t>
+          <t>Fundamentals of Regression Analysis</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -4748,7 +4749,7 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/getting-started-with-deep-learning</t>
+          <t>https://www.analyticsvidhya.com/courses/Fundamentals-of-Regression-Analysis</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -4758,7 +4759,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Getting Started with Deep Learning (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Fundamentals of Regression Analysis (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -4773,7 +4774,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Getting Started With Large Language Models</t>
+          <t>Getting Started with Deep Learning</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4788,7 +4789,7 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/getting-started-with-llms</t>
+          <t>https://www.analyticsvidhya.com/courses/getting-started-with-deep-learning</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -4798,7 +4799,7 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Getting Started With Large Language Models (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Getting Started with Deep Learning (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -4813,7 +4814,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Introduction to AI &amp; ML</t>
+          <t>Getting Started With Large Language Models</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -4828,7 +4829,7 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/introduction-to-ai-ml</t>
+          <t>https://www.analyticsvidhya.com/courses/getting-started-with-llms</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -4838,7 +4839,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Introduction to AI &amp; ML (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Getting Started With Large Language Models (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -4853,7 +4854,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Introduction to Transformers and Attention Mechanisms</t>
+          <t>Introduction to AI &amp; ML</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4868,7 +4869,7 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/introduction-to-transformers-and-attention-mechanisms</t>
+          <t>https://www.analyticsvidhya.com/courses/introduction-to-ai-ml</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -4878,7 +4879,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Introduction to Transformers and Attention Mechanisms (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Introduction to AI &amp; ML (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -4893,7 +4894,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>K-Nearest Neighbors (KNN) Algorithm in Python and R</t>
+          <t>Introduction to Transformers and Attention Mechanisms</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -4908,7 +4909,7 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/K-Nearest-Neighbors-KNN-Algorithm</t>
+          <t>https://www.analyticsvidhya.com/courses/introduction-to-transformers-and-attention-mechanisms</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -4918,7 +4919,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: K-Nearest Neighbors (KNN) Algorithm in Python and R (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Introduction to Transformers and Attention Mechanisms (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -4933,7 +4934,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning Certification course for Beginners</t>
+          <t>K-Nearest Neighbors (KNN) Algorithm in Python and R</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -4948,7 +4949,7 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/machine-learning-certification-program-beginners</t>
+          <t>https://www.analyticsvidhya.com/courses/K-Nearest-Neighbors-KNN-Algorithm</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -4958,7 +4959,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Machine Learning Certification course for Beginners (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: K-Nearest Neighbors (KNN) Algorithm in Python and R (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -4973,7 +4974,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Naive Bayes from Scratch</t>
+          <t>Machine Learning Certification course for Beginners</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -4988,7 +4989,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/naive-bayes</t>
+          <t>https://www.analyticsvidhya.com/courses/machine-learning-certification-program-beginners</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -4998,7 +4999,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Naive Bayes from Scratch (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Machine Learning Certification course for Beginners (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -5013,7 +5014,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>The A to Z of Unsupervised ML</t>
+          <t>Naive Bayes from Scratch</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -5028,7 +5029,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/free-unsupervised-ml-guide</t>
+          <t>https://www.analyticsvidhya.com/courses/naive-bayes</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5038,7 +5039,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: The A to Z of Unsupervised ML (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Naive Bayes from Scratch (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -5053,7 +5054,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Understanding Linear Regression</t>
+          <t>The A to Z of Unsupervised ML</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -5068,7 +5069,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/free-understanding-linear-regression</t>
+          <t>https://www.analyticsvidhya.com/courses/free-unsupervised-ml-guide</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -5078,7 +5079,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Understanding Linear Regression (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: The A to Z of Unsupervised ML (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -5093,7 +5094,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Understanding the working of Neural Networks</t>
+          <t>Understanding Linear Regression</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -5108,7 +5109,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/understanding-the-working-of-neural-networks</t>
+          <t>https://www.analyticsvidhya.com/courses/free-understanding-linear-regression</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5118,7 +5119,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Understanding the working of Neural Networks (Machine Learning &amp; Deep Learning Course)</t>
+          <t>Comprehensive free training course: Understanding Linear Regression (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -5133,12 +5134,12 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Google Skillshop</t>
+          <t>Understanding the working of Neural Networks</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Official Google Training</t>
+          <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -5148,7 +5149,7 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>https://skillshop.withgoogle.com</t>
+          <t>https://www.analyticsvidhya.com/courses/understanding-the-working-of-neural-networks</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5158,12 +5159,12 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Google Skillshop (Official Google Training)</t>
+          <t>Comprehensive free training course: Understanding the working of Neural Networks (Machine Learning &amp; Deep Learning Course)</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Google)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5174,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Coursera – Generative AI for Everyone</t>
+          <t>Google Skillshop</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Online Course</t>
+          <t>Official Google Training</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -5188,22 +5189,22 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://www.coursera.org/learn/generative-ai-for-everyone</t>
+          <t>https://skillshop.withgoogle.com</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Coursera – Generative AI for Everyone (Online Course)</t>
+          <t>Free education and certified training: Google Skillshop (Official Google Training)</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Google)</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5214,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Coursera – Generative AI with LLMs</t>
+          <t>Coursera – Generative AI for Everyone</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5228,7 +5229,7 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>https://www.coursera.org/learn/generative-ai-with-llms</t>
+          <t>https://www.coursera.org/learn/generative-ai-for-everyone</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -5238,7 +5239,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Coursera – Generative AI with LLMs (Online Course)</t>
+          <t>Free education and certified training: Coursera – Generative AI for Everyone (Online Course)</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -5253,7 +5254,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Coursera – Machine Learning</t>
+          <t>Coursera – Generative AI with LLMs</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -5268,7 +5269,7 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://www.coursera.org/learn/machine-learning</t>
+          <t>https://www.coursera.org/learn/generative-ai-with-llms</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -5278,12 +5279,12 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Coursera – Machine Learning (Online Course)</t>
+          <t>Free education and certified training: Coursera – Generative AI with LLMs (Online Course)</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Machine Learning)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5294,12 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Great Learning Academy</t>
+          <t>Coursera – Machine Learning</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Online Course Platform</t>
+          <t>Online Course</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -5308,22 +5309,22 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>https://www.mygreatlearning.com/academy</t>
+          <t>https://www.coursera.org/learn/machine-learning</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Great Learning Academy (Online Course Platform)</t>
+          <t>Free education and certified training: Coursera – Machine Learning (Online Course)</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Data Analysis)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Machine Learning)</t>
         </is>
       </c>
     </row>
@@ -5333,12 +5334,12 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>GitHub – Microsoft Generative AI for Beginners</t>
+          <t>Great Learning Academy</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Open Source AI Course</t>
+          <t>Online Course Platform</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -5348,7 +5349,7 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/generative-ai-for-beginners</t>
+          <t>https://www.mygreatlearning.com/academy</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -5358,12 +5359,12 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: GitHub – Microsoft Generative AI for Beginners (Open Source AI Course)</t>
+          <t>Free education and certified training: Great Learning Academy (Online Course Platform)</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Data Analysis)</t>
         </is>
       </c>
     </row>
@@ -5373,12 +5374,12 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Coursera – Google Data Analytics</t>
+          <t>GitHub – Microsoft Generative AI for Beginners</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Professional Certificate</t>
+          <t>Open Source AI Course</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -5388,22 +5389,22 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>https://www.coursera.org/professional-certificates/google-data-analytics</t>
+          <t>https://github.com/microsoft/generative-ai-for-beginners</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: Coursera – Google Data Analytics (Professional Certificate)</t>
+          <t>Free education and certified training: GitHub – Microsoft Generative AI for Beginners (Open Source AI Course)</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Data Analysis)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Ai)</t>
         </is>
       </c>
     </row>
@@ -5413,12 +5414,12 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Big Mart Sales Prediction Using R</t>
+          <t>Coursera – Google Data Analytics</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Project-Based Learning Course</t>
+          <t>Professional Certificate</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -5428,22 +5429,22 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/big-mart-sales-prediction-using-r</t>
+          <t>https://www.coursera.org/professional-certificates/google-data-analytics</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Big Mart Sales Prediction Using R (Project-Based Learning Course)</t>
+          <t>Free education and certified training: Coursera – Google Data Analytics (Professional Certificate)</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Data Analysis)</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5454,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Build Data Pipelines with Apache Airflow</t>
+          <t>Big Mart Sales Prediction Using R</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -5468,7 +5469,7 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/build-data-pipelines-with-apache-airflow</t>
+          <t>https://www.analyticsvidhya.com/courses/big-mart-sales-prediction-using-r</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -5478,7 +5479,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Build Data Pipelines with Apache Airflow (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: Big Mart Sales Prediction Using R (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -5493,7 +5494,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Building a Deep Research AI Agent</t>
+          <t>Build Data Pipelines with Apache Airflow</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -5508,7 +5509,7 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/building-a-deep-research-ai-agent</t>
+          <t>https://www.analyticsvidhya.com/courses/build-data-pipelines-with-apache-airflow</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -5518,7 +5519,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Building a Deep Research AI Agent (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: Build Data Pipelines with Apache Airflow (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -5533,7 +5534,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Coding a ChatGPT-style Language Model From Scratch in Pytorch</t>
+          <t>Building a Deep Research AI Agent</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -5548,7 +5549,7 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/coding-a-chatgpt-style-language-model-from-scratch-in-pytorch</t>
+          <t>https://www.analyticsvidhya.com/courses/building-a-deep-research-ai-agent</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -5558,7 +5559,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Coding a ChatGPT-style Language Model From Scratch in Pytorch (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: Building a Deep Research AI Agent (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -5573,7 +5574,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>How to Build an Image Generator Web App with Zero Coding</t>
+          <t>Coding a ChatGPT-style Language Model From Scratch in Pytorch</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -5588,7 +5589,7 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/how-to-build-an-image-generator-web-app-with-zero-coding</t>
+          <t>https://www.analyticsvidhya.com/courses/coding-a-chatgpt-style-language-model-from-scratch-in-pytorch</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -5598,7 +5599,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: How to Build an Image Generator Web App with Zero Coding (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: Coding a ChatGPT-style Language Model From Scratch in Pytorch (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -5613,7 +5614,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Loan Prediction Practice Problem (Using Python)</t>
+          <t>How to Build an Image Generator Web App with Zero Coding</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -5628,7 +5629,7 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/loan-prediction-practice-problem-using-python</t>
+          <t>https://www.analyticsvidhya.com/courses/how-to-build-an-image-generator-web-app-with-zero-coding</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -5638,7 +5639,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Loan Prediction Practice Problem (Using Python) (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: How to Build an Image Generator Web App with Zero Coding (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -5653,7 +5654,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Model Deployment using FastAPI</t>
+          <t>Loan Prediction Practice Problem (Using Python)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -5668,7 +5669,7 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/model-deployment-using-fastapi</t>
+          <t>https://www.analyticsvidhya.com/courses/loan-prediction-practice-problem-using-python</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -5678,7 +5679,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Model Deployment using FastAPI (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: Loan Prediction Practice Problem (Using Python) (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -5693,7 +5694,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>OpenEngage: Build a complete AI Driven Marketing Engine</t>
+          <t>Model Deployment using FastAPI</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5708,7 +5709,7 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/openengage-a-complete-ai-driven-marketing-engine</t>
+          <t>https://www.analyticsvidhya.com/courses/model-deployment-using-fastapi</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -5718,7 +5719,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: OpenEngage: Build a complete AI Driven Marketing Engine (Project-Based Learning Course)</t>
+          <t>Comprehensive free training course: Model Deployment using FastAPI (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -5733,12 +5734,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Build a Document Retriever Search Engine with LangChain</t>
+          <t>OpenEngage: Build a complete AI Driven Marketing Engine</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>RAG Application Course</t>
+          <t>Project-Based Learning Course</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -5748,7 +5749,7 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/build-a-document-retriever-search-engine-with-langchain</t>
+          <t>https://www.analyticsvidhya.com/courses/openengage-a-complete-ai-driven-marketing-engine</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -5758,7 +5759,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Build a Document Retriever Search Engine with LangChain (RAG Application Course)</t>
+          <t>Comprehensive free training course: OpenEngage: Build a complete AI Driven Marketing Engine (Project-Based Learning Course)</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -5773,7 +5774,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Build your first RAG system using Llamaindex</t>
+          <t>Build a Document Retriever Search Engine with LangChain</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -5788,7 +5789,7 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/building-first-rag-systems-using-llamaindex</t>
+          <t>https://www.analyticsvidhya.com/courses/build-a-document-retriever-search-engine-with-langchain</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -5798,7 +5799,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Build your first RAG system using Llamaindex (RAG Application Course)</t>
+          <t>Comprehensive free training course: Build a Document Retriever Search Engine with LangChain (RAG Application Course)</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -5813,7 +5814,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>End to end RAG Application Development with LangChain and Streamlit</t>
+          <t>Build your first RAG system using Llamaindex</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5828,7 +5829,7 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/end-to-end-app-rag-application-development-with-langchain-and-streamlit</t>
+          <t>https://www.analyticsvidhya.com/courses/building-first-rag-systems-using-llamaindex</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -5838,7 +5839,7 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: End to end RAG Application Development with LangChain and Streamlit (RAG Application Course)</t>
+          <t>Comprehensive free training course: Build your first RAG system using Llamaindex (RAG Application Course)</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -5853,7 +5854,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Improving Real World RAG Systems :Key Challenges</t>
+          <t>End to end RAG Application Development with LangChain and Streamlit</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5868,7 +5869,7 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/improving-real-world-rag-systems-key-challenges</t>
+          <t>https://www.analyticsvidhya.com/courses/end-to-end-app-rag-application-development-with-langchain-and-streamlit</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -5878,7 +5879,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Improving Real World RAG Systems :Key Challenges (RAG Application Course)</t>
+          <t>Comprehensive free training course: End to end RAG Application Development with LangChain and Streamlit (RAG Application Course)</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -5893,7 +5894,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Mastering Multimodal RAG &amp; Embeddings with Amazon Nova &amp; Bedrock</t>
+          <t>Improving Real World RAG Systems :Key Challenges</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5908,7 +5909,7 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/mastering-multimodal-rag-and-embeddings-with-amazon-nova-and-bedrock</t>
+          <t>https://www.analyticsvidhya.com/courses/improving-real-world-rag-systems-key-challenges</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -5918,7 +5919,7 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Mastering Multimodal RAG &amp; Embeddings with Amazon Nova &amp; Bedrock (RAG Application Course)</t>
+          <t>Comprehensive free training course: Improving Real World RAG Systems :Key Challenges (RAG Application Course)</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -5933,12 +5934,12 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>LearnVern</t>
+          <t>Mastering Multimodal RAG &amp; Embeddings with Amazon Nova &amp; Bedrock</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Skill Development Platform</t>
+          <t>RAG Application Course</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -5948,22 +5949,22 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>https://www.learnvern.com</t>
+          <t>https://www.analyticsvidhya.com/courses/mastering-multimodal-rag-and-embeddings-with-amazon-nova-and-bedrock</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: LearnVern (Skill Development Platform)</t>
+          <t>Comprehensive free training course: Mastering Multimodal RAG &amp; Embeddings with Amazon Nova &amp; Bedrock (RAG Application Course)</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Skill Based)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5974,12 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>STP Computer Education – Notes</t>
+          <t>LearnVern</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Study Notes / Learning Material</t>
+          <t>Skill Development Platform</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -5988,22 +5989,22 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://www.stpcomputereducation.com/notes</t>
+          <t>https://www.learnvern.com</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: STP Computer Education – Notes (Study Notes / Learning Material)</t>
+          <t>Free education and certified training: LearnVern (Skill Development Platform)</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Computer)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Skill Based)</t>
         </is>
       </c>
     </row>
@@ -6013,12 +6014,12 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Building a Customized Newsletter AI Agent</t>
+          <t>STP Computer Education – Notes</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Vibe Coding Course</t>
+          <t>Study Notes / Learning Material</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -6028,7 +6029,7 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/building-a-customized-newsletter-ai-agent</t>
+          <t>https://www.stpcomputereducation.com/notes</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -6038,12 +6039,12 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Building a Customized Newsletter AI Agent (Vibe Coding Course)</t>
+          <t>Free education and certified training: STP Computer Education – Notes (Study Notes / Learning Material)</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Computer)</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6054,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Guide to Vibe Coding in Windsurf</t>
+          <t>Building a Customized Newsletter AI Agent</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -6068,7 +6069,7 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/guide-to-vibe-coding-in-windsurf</t>
+          <t>https://www.analyticsvidhya.com/courses/building-a-customized-newsletter-ai-agent</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -6078,7 +6079,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Guide to Vibe Coding in Windsurf (Vibe Coding Course)</t>
+          <t>Comprehensive free training course: Building a Customized Newsletter AI Agent (Vibe Coding Course)</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -6093,7 +6094,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>n8n - A Complete Guide to Automation Tool</t>
+          <t>Guide to Vibe Coding in Windsurf</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6108,7 +6109,7 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/n8n-a-complete-guide-to-the-automation-tool</t>
+          <t>https://www.analyticsvidhya.com/courses/guide-to-vibe-coding-in-windsurf</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -6118,7 +6119,7 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: n8n - A Complete Guide to Automation Tool (Vibe Coding Course)</t>
+          <t>Comprehensive free training course: Guide to Vibe Coding in Windsurf (Vibe Coding Course)</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -6133,7 +6134,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Vibe Coding with Replit</t>
+          <t>n8n - A Complete Guide to Automation Tool</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -6148,7 +6149,7 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://www.analyticsvidhya.com/courses/vibe-coding-with-replit</t>
+          <t>https://www.analyticsvidhya.com/courses/n8n-a-complete-guide-to-the-automation-tool</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -6158,7 +6159,7 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive free training course: Vibe Coding with Replit (Vibe Coding Course)</t>
+          <t>Comprehensive free training course: n8n - A Complete Guide to Automation Tool (Vibe Coding Course)</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -6173,12 +6174,12 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>STP Computer Education – Web Development</t>
+          <t>Vibe Coding with Replit</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Web Development Course</t>
+          <t>Vibe Coding Course</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -6188,22 +6189,22 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>https://www.stpcomputereducation.com/courses/web-development.html</t>
+          <t>https://www.analyticsvidhya.com/courses/vibe-coding-with-replit</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: STP Computer Education – Web Development (Web Development Course)</t>
+          <t>Comprehensive free training course: Vibe Coding with Replit (Vibe Coding Course)</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🎓 Course Library.xlsx (Computer)</t>
+          <t>Excel: 🎓 Course Library.xlsx (Sheet1)</t>
         </is>
       </c>
     </row>
@@ -6213,37 +6214,37 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>PDF Chef (Mobile)</t>
+          <t>STP Computer Education – Web Development</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Mobile PDF Tool</t>
+          <t>Web Development Course</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>📄 PDF &amp; Document Utilities</t>
+          <t>🎓 Free Courses &amp; Learning Platforms</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://play.google.com/store/apps/details?id=com.dhananjaytech.pdfchef</t>
+          <t>https://www.stpcomputereducation.com/courses/web-development.html</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Offline PDF management and conversion app</t>
+          <t>Free education and certified training: STP Computer Education – Web Development (Web Development Course)</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Excel: 📄 PDF Resources.xlsx</t>
+          <t>Excel: 🎓 Course Library.xlsx (Computer)</t>
         </is>
       </c>
     </row>
@@ -6253,12 +6254,12 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Sejda PDF</t>
+          <t>PDF Chef (Mobile)</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Online PDF Editor</t>
+          <t>Mobile PDF Tool</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -6268,17 +6269,17 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>https://www.sejda.com</t>
+          <t>https://play.google.com/store/apps/details?id=com.dhananjaytech.pdfchef</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Online PDF editor, merge, split, and conversion tools</t>
+          <t>Offline PDF management and conversion app</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -6293,12 +6294,12 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>tinywow.com</t>
+          <t>TinyWow</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Productivity Tool</t>
+          <t>Multi-Tool Suite</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -6318,7 +6319,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>Swiss Army knife of 200+ free online tools for PDF image video and file conversions</t>
+          <t>Free online tools for PDF, video, image, and document conversion</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -6333,22 +6334,22 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>coddy.tech</t>
+          <t>Sejda PDF</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Developer &amp; Code Utility</t>
+          <t>Online PDF Editor</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Web Utilities &amp; Productivity</t>
+          <t>📄 PDF &amp; Document Utilities</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>https://coddy.tech</t>
+          <t>https://www.sejda.com</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -6358,12 +6359,12 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Bite-sized coding lessons you complete in your browser with instant feedback</t>
+          <t>Online PDF editor, merge, split, and conversion tools</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 📄 PDF Resources.xlsx</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6374,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>internet-janitor.itch.io</t>
+          <t>coddy.tech</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -6388,17 +6389,17 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://internet-janitor.itch.io</t>
+          <t>https://coddy.tech</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>Tool for making interactive fiction and clicky experiences without learning a game engine</t>
+          <t>Bite-sized coding lessons you complete in your browser with instant feedback</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -6413,7 +6414,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>learn-anything.xyz</t>
+          <t>internet-janitor.itch.io</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -6428,7 +6429,7 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>https://learn-anything.xyz</t>
+          <t>https://internet-janitor.itch.io</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6438,7 +6439,7 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Curated learning paths for any topic - community-organized roadmaps instead of random tutorials</t>
+          <t>Tool for making interactive fiction and clicky experiences without learning a game engine</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -6453,7 +6454,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>n8n.io</t>
+          <t>learn-anything.xyz</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -6468,17 +6469,17 @@
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://n8n.io</t>
+          <t>https://learn-anything.xyz</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>Open-source workflow automation that connects apps and automates tasks with visual builder</t>
+          <t>Curated learning paths for any topic - community-organized roadmaps instead of random tutorials</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -6493,7 +6494,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>roadmap.sh</t>
+          <t>n8n.io</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -6508,17 +6509,17 @@
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>https://roadmap.sh</t>
+          <t>https://n8n.io</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Developer career learning paths with step-by-step roadmaps for any tech specialization</t>
+          <t>Open-source workflow automation that connects apps and automates tasks with visual builder</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -6533,7 +6534,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>topoexport.com</t>
+          <t>roadmap.sh</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -6548,17 +6549,17 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://topoexport.com</t>
+          <t>https://roadmap.sh</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>Export 3D terrain models from anywhere on Earth for 3D printing or game development</t>
+          <t>Developer career learning paths with step-by-step roadmaps for any tech specialization</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -6573,12 +6574,12 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>10015 Tools</t>
+          <t>topoexport.com</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Developer Tools</t>
+          <t>Developer &amp; Code Utility</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -6588,22 +6589,22 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>https://10015.io</t>
+          <t>https://topoexport.com</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Developer Tools</t>
+          <t>Export 3D terrain models from anywhere on Earth for 3D printing or game development</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6614,12 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>1aauto.com</t>
+          <t>10015 Tools</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>DIY Vehicle Repair Guides</t>
+          <t>Developer Tools</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -6628,7 +6629,7 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://1aauto.com</t>
+          <t>https://10015.io</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -6638,12 +6639,12 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>Free DIY car repair video guides showing step-by-step fixes for common vehicle problems</t>
+          <t>High-utility web tool: Developer Tools</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -6653,12 +6654,12 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>FilePursuit</t>
+          <t>1aauto.com</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>File Search Engine</t>
+          <t>DIY Vehicle Repair Guides</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -6668,7 +6669,7 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>https://filepursuit.com</t>
+          <t>https://1aauto.com</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -6678,12 +6679,12 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: File Search Engine</t>
+          <t>Free DIY car repair video guides showing step-by-step fixes for common vehicle problems</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -6693,12 +6694,12 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Flightradar24</t>
+          <t>FilePursuit</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Flight Tracking</t>
+          <t>File Search Engine</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -6708,22 +6709,22 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://www.flightradar24.com</t>
+          <t>https://filepursuit.com</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Flight Tracking</t>
+          <t>High-speed online tool: File Search Engine</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6734,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>MrFreeTools</t>
+          <t>Flightradar24</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Free Online Tools</t>
+          <t>Flight Tracking</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -6748,17 +6749,17 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>https://mrfreetools.com</t>
+          <t>https://www.flightradar24.com</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Free Online Tools</t>
+          <t>High-utility web tool: Flight Tracking</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -6773,12 +6774,12 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ifixit.com</t>
+          <t>MrFreeTools</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Hardware &amp; Device Repair Guides</t>
+          <t>Free Online Tools</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -6788,7 +6789,7 @@
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://ifixit.com</t>
+          <t>https://mrfreetools.com</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -6798,12 +6799,12 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>Free repair guides for phones laptops and appliances - fix it yourself and save money</t>
+          <t>High-utility web tool: Free Online Tools</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6814,12 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>PI7 Image Tool</t>
+          <t>ifixit.com</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Image Processing Tool</t>
+          <t>Hardware &amp; Device Repair Guides</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -6828,7 +6829,7 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>https://image.pi7.org</t>
+          <t>https://ifixit.com</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -6838,12 +6839,12 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Image Processing Tool</t>
+          <t>Free repair guides for phones laptops and appliances - fix it yourself and save money</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -6853,12 +6854,12 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>123Apps</t>
+          <t>PI7 Image Tool</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Online Utility Tools</t>
+          <t>Image Processing Tool</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -6868,7 +6869,7 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://123apps.com</t>
+          <t>https://image.pi7.org</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -6878,12 +6879,12 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Online Utility Tools</t>
+          <t>High-speed online tool: Image Processing Tool</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -6893,12 +6894,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>archive.ph</t>
+          <t>123Apps</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Permanent Web Archiving Utility</t>
+          <t>Online Utility Tools</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -6908,7 +6909,7 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>https://archive.ph</t>
+          <t>https://123apps.com</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -6918,12 +6919,12 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>Save permanent copies of web pages before they change or disappear forever</t>
+          <t>High-utility web tool: Online Utility Tools</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6934,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>autocatalogarchive.com</t>
+          <t>archive.ph</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -6948,7 +6949,7 @@
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://autocatalogarchive.com</t>
+          <t>https://archive.ph</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -6958,7 +6959,7 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>Archive of vintage car brochures and catalogs for classic vehicle research and nostalgia</t>
+          <t>Save permanent copies of web pages before they change or disappear forever</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -6973,12 +6974,12 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>fakeupdate.net</t>
+          <t>autocatalogarchive.com</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Productivity Tool</t>
+          <t>Permanent Web Archiving Utility</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -6988,7 +6989,7 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>https://fakeupdate.net</t>
+          <t>https://autocatalogarchive.com</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -6998,7 +6999,7 @@
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>Fake system update screens perfect for office pranks or looking busy during meetings</t>
+          <t>Archive of vintage car brochures and catalogs for classic vehicle research and nostalgia</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -7013,7 +7014,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>haveibeenpwned.com</t>
+          <t>fakeupdate.net</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -7028,7 +7029,7 @@
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://haveibeenpwned.com</t>
+          <t>https://fakeupdate.net</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -7038,7 +7039,7 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>Check if your email or password appeared in data breaches - everyone should use this</t>
+          <t>Fake system update screens perfect for office pranks or looking busy during meetings</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -7053,7 +7054,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>makemydrivefun.com</t>
+          <t>haveibeenpwned.com</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -7068,7 +7069,7 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>https://makemydrivefun.com</t>
+          <t>https://haveibeenpwned.com</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -7078,7 +7079,7 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>Find quirky roadside attractions and interesting detours along your planned driving route</t>
+          <t>Check if your email or password appeared in data breaches - everyone should use this</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -7093,7 +7094,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ssemble.com</t>
+          <t>makemydrivefun.com</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -7108,17 +7109,17 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://ssemble.com</t>
+          <t>https://makemydrivefun.com</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>Browser-based video editor with AI features for creating and editing without downloads</t>
+          <t>Find quirky roadside attractions and interesting detours along your planned driving route</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -7133,7 +7134,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>stirlingpdf.io</t>
+          <t>ssemble.com</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -7148,17 +7149,17 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>https://stirlingpdf.io</t>
+          <t>https://ssemble.com</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>Open-source all-in-one PDF manipulation tool you can self-host for privacy</t>
+          <t>Browser-based video editor with AI features for creating and editing without downloads</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -7173,7 +7174,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>trace.moe</t>
+          <t>stirlingpdf.io</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -7188,7 +7189,7 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://trace.moe</t>
+          <t>https://stirlingpdf.io</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -7198,7 +7199,7 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>Reverse image search for anime that identifies the exact scene from any screenshot</t>
+          <t>Open-source all-in-one PDF manipulation tool you can self-host for privacy</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -7213,7 +7214,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>unpigeon.me</t>
+          <t>trace.moe</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -7228,7 +7229,7 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>https://unpigeon.me</t>
+          <t>https://trace.moe</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -7238,7 +7239,7 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>Convert email newsletter subscriptions to RSS feeds to escape inbox clutter</t>
+          <t>Reverse image search for anime that identifies the exact scene from any screenshot</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -7253,7 +7254,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>versus.com</t>
+          <t>unpigeon.me</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -7268,7 +7269,7 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://versus.com</t>
+          <t>https://unpigeon.me</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7278,7 +7279,7 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side product comparisons with detailed spec breakdowns across phones laptops and more</t>
+          <t>Convert email newsletter subscriptions to RSS feeds to escape inbox clutter</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -7293,12 +7294,12 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Useful Free Online Tools &amp; Sites</t>
+          <t>versus.com</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Tool Collection (GitHub)</t>
+          <t>Productivity Tool</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -7308,7 +7309,7 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/J0rgeSerran0/Useful-Free-Online-Tools-and-Sites</t>
+          <t>https://versus.com</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -7318,12 +7319,12 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Tool Collection (GitHub)</t>
+          <t>Side-by-side product comparisons with detailed spec breakdowns across phones laptops and more</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7334,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>drivenlisten.com</t>
+          <t>Useful Free Online Tools &amp; Sites</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Utility Tool</t>
+          <t>Tool Collection (GitHub)</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -7348,7 +7349,7 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://drivenlisten.com</t>
+          <t>https://github.com/J0rgeSerran0/Useful-Free-Online-Tools-and-Sites</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -7358,12 +7359,12 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Virtual drives through cities worldwide with real dashcam footage and local radio</t>
+          <t>High-utility web tool: Tool Collection (GitHub)</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7374,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>entertrained.app</t>
+          <t>drivenlisten.com</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -7388,7 +7389,7 @@
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>https://entertrained.app</t>
+          <t>https://drivenlisten.com</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -7398,7 +7399,7 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>Practice typing by retyping classic books - skill building while reading great literature</t>
+          <t>Virtual drives through cities worldwide with real dashcam footage and local radio</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -7413,7 +7414,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>freesewing.eu</t>
+          <t>entertrained.app</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -7428,7 +7429,7 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://freesewing.eu</t>
+          <t>https://entertrained.app</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7438,7 +7439,7 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Generate custom sewing patterns from your exact body measurements - open source and free</t>
+          <t>Practice typing by retyping classic books - skill building while reading great literature</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -7453,7 +7454,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>mcbroken.com</t>
+          <t>freesewing.eu</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -7468,7 +7469,7 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>https://mcbroken.com</t>
+          <t>https://freesewing.eu</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -7478,7 +7479,7 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Check if the McDonald's ice cream machine near you is working before you drive there</t>
+          <t>Generate custom sewing patterns from your exact body measurements - open source and free</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -7493,7 +7494,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>myfridgefood.com</t>
+          <t>mcbroken.com</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -7508,7 +7509,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://myfridgefood.com</t>
+          <t>https://mcbroken.com</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -7518,7 +7519,7 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Recipe finder that suggests meals based on ingredients you already have at home</t>
+          <t>Check if the McDonald's ice cream machine near you is working before you drive there</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -7533,7 +7534,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>onelook.com</t>
+          <t>myfridgefood.com</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -7548,7 +7549,7 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>https://onelook.com</t>
+          <t>https://myfridgefood.com</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -7558,7 +7559,7 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Reverse dictionary that finds words when you only know the definition or concept</t>
+          <t>Recipe finder that suggests meals based on ingredients you already have at home</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -7573,7 +7574,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>pointerpointer.com</t>
+          <t>onelook.com</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -7588,7 +7589,7 @@
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://pointerpointer.com</t>
+          <t>https://onelook.com</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -7598,7 +7599,7 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>Whimsical website that finds photos of people pointing exactly where your cursor is</t>
+          <t>Reverse dictionary that finds words when you only know the definition or concept</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -7613,7 +7614,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>roadtrippers.com</t>
+          <t>pointerpointer.com</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -7628,17 +7629,17 @@
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>https://roadtrippers.com</t>
+          <t>https://pointerpointer.com</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Road trip planning tool with stops attractions and route optimization all in one</t>
+          <t>Whimsical website that finds photos of people pointing exactly where your cursor is</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -7653,7 +7654,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>wifimap.io</t>
+          <t>roadtrippers.com</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -7668,7 +7669,7 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://wifimap.io</t>
+          <t>https://roadtrippers.com</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -7678,7 +7679,7 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>Crowdsourced database of WiFi passwords from cafes airports and public places worldwide</t>
+          <t>Road trip planning tool with stops attractions and route optimization all in one</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -7693,12 +7694,12 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Website Planet Tools</t>
+          <t>wifimap.io</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Web Utilities</t>
+          <t>Utility Tool</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -7708,22 +7709,22 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>https://www.websiteplanet.com/webtools</t>
+          <t>https://wifimap.io</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Web Utilities</t>
+          <t>Crowdsourced database of WiFi passwords from cafes airports and public places worldwide</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -7733,12 +7734,12 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>xTiles</t>
+          <t>Website Planet Tools</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Workspace / Productivity</t>
+          <t>Web Utilities</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -7748,17 +7749,17 @@
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://xtiles.app/workspace/personal</t>
+          <t>https://www.websiteplanet.com/webtools</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Workspace / Productivity</t>
+          <t>High-utility web tool: Web Utilities</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -7773,37 +7774,37 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>3dtuning.com</t>
+          <t>xTiles</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>3D Virtual Vehicle Customizer</t>
+          <t>Workspace / Productivity</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>🎨 Design &amp; Creator Tools</t>
+          <t>🛠️ Web Utilities &amp; Productivity</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>https://3dtuning.com</t>
+          <t>https://xtiles.app/workspace/personal</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>Virtual car customization tool to visualize modifications and dream builds before spending money</t>
+          <t>High-utility web tool: Workspace / Productivity</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7814,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>carcarekiosk.com</t>
+          <t>3dtuning.com</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -7828,17 +7829,17 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://carcarekiosk.com</t>
+          <t>https://3dtuning.com</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>Vehicle-specific maintenance video tutorials for your exact car make and model</t>
+          <t>Virtual car customization tool to visualize modifications and dream builds before spending money</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -7853,7 +7854,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>dora.run</t>
+          <t>carcarekiosk.com</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -7868,17 +7869,17 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>https://dora.run</t>
+          <t>https://carcarekiosk.com</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>No-code builder for impressive 3D animated websites without learning WebGL or Three.js</t>
+          <t>Vehicle-specific maintenance video tutorials for your exact car make and model</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -7893,7 +7894,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>home.by.me</t>
+          <t>dora.run</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -7908,7 +7909,7 @@
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://home.by.me</t>
+          <t>https://dora.run</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -7918,7 +7919,7 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>3D home design and room planner to visualize renovations before committing to changes</t>
+          <t>No-code builder for impressive 3D animated websites without learning WebGL or Three.js</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -7933,7 +7934,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>pacdora.com</t>
+          <t>home.by.me</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -7948,7 +7949,7 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>https://pacdora.com</t>
+          <t>https://home.by.me</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -7958,7 +7959,7 @@
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>3D packaging mockup generator for product branding with realistic visualization</t>
+          <t>3D home design and room planner to visualize renovations before committing to changes</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -7973,7 +7974,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Radio Garden</t>
+          <t>pacdora.com</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -7988,22 +7989,22 @@
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://radio.garden</t>
+          <t>https://pacdora.com</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>Interactive 3D globe allowing users to rotate the earth and tune into live radio stations worldwide.</t>
+          <t>3D packaging mockup generator for product branding with realistic visualization</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>User Chat Prompt</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -9724,6 +9725,1023 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Website Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Website Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Official URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>3dtuning.com</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>https://3dtuning.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Virtual car customization tool to visualize modifications and dream builds before spending money</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>carcarekiosk.com</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>https://carcarekiosk.com</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Vehicle-specific maintenance video tutorials for your exact car make and model</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>dora.run</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>https://dora.run</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>No-code builder for impressive 3D animated websites without learning WebGL or Three.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>home.by.me</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>https://home.by.me</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>3D home design and room planner to visualize renovations before committing to changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>pacdora.com</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>https://pacdora.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>3D packaging mockup generator for product branding with realistic visualization</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>startmycar.com</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>https://startmycar.com</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Car troubleshooting guide that helps diagnose why your car won't start with solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>uiverse.io</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>3D Virtual Vehicle Customizer</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>https://uiverse.io</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Community-driven library of free open-source UI elements including buttons cards and loaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>jitter.video</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Browser-Based Video Editor</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>https://jitter.video</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Browser-based motion graphics editor for designers who don't want to learn After Effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>musclewiki.com</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Browser-Based Video Editor</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>https://musclewiki.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Interactive muscle map showing exercises for every body part with video demonstrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>whitescreen.online</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Browser-Based Video Editor</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://whitescreen.online</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Full-screen color display for testing monitors lighting video calls or cleaning screens</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>clicktheredbutton.com</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Creative Design Platform</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://clicktheredbutton.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Random weird website discovery tool - click and find something unexpected on the internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>dreamforth.com</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Creative Design Platform</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://dreamforth.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Dream interpretation dictionary to explore what your vivid or recurring dreams might mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>fragrantica.com</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Creative Design Platform</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>https://fragrantica.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Comprehensive perfume database with detailed notes and community reviews before you buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>music-map.com</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Creative Design Platform</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://music-map.com</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Discover similar artists visualized as a spatial map - type any band and explore</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>nullfake.com</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Creative Design Platform</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>https://nullfake.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Detect fake Amazon reviews and see adjusted ratings based only on authentic reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>supercook.com</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Creative Design Platform</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://supercook.com</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Recipe search engine that finds dishes you can make with ingredients you already have</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>flourish.studio</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>https://flourish.studio</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Create beautiful interactive data visualizations and charts without knowing how to code</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>framer.com</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://framer.com</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>No-code website builder with pixel-perfect control for designers who want professional results</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>planyourroom.com</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>https://planyourroom.com</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Drag-and-drop room layout planner to test furniture arrangements before buying or moving</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>pngimg.com</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>https://pngimg.com</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Free database of PNG images with transparent backgrounds ready for design projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>reactbits.dev</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>https://reactbits.dev</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Collection of animated React components ready to copy and paste into your projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>squoosh.app</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>https://squoosh.app</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Google's image compression tool with side-by-side comparison to optimize file sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>sweezy-cursors.com</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>https://sweezy-cursors.com</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Custom animated browser cursors with hundreds of themed and animated styles to choose</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>tailornova.com</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>https://tailornova.com</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Generate custom sewing patterns made-to-measure from your exact body measurements</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>thetruesize.com</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>https://thetruesize.com</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Interactive map showing true size of countries by correcting Mercator projection distortions</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>typefaceanimator.com</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>https://typefaceanimator.com</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Browser tool for creating animated typeface transitions and kinetic typography effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>uiball.com</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Design Design Platform</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>https://uiball.com</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Free collection of beautiful loading spinners and UI loaders for modern web projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>animejs.com</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>JavaScript Web Animation Engine</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>https://animejs.com</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Lightweight JavaScript animation library for smooth web animations without heavy dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>paperanimator.com</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>JavaScript Web Animation Engine</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>https://paperanimator.com</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Turn hand-drawn character sketches into animations with simple drag-and-drop rigging</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>hyperpost.studio</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Social Media Template Booster</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>https://hyperpost.studio</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Social media template booster packs</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>thetoymaker.com</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Social Media Template Booster</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>https://thetoymaker.com</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Printable paper toy templates you can cut fold and glue into whimsical 3D figures</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10456,6 +11474,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Website Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Website Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Official URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Radio Garden</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Online Radio Map</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>https://radio.garden</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Interactive 3D globe allowing users to rotate the earth and tune into live radio stations worldwide.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10692,7 +11797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11151,7 +12256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12013,7 +13118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12998,7 +14103,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>YouTube – ES4TpVsTkgc</t>
+          <t>YouTube – dLKPBSov2F4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -13018,7 +14123,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Free education and certified training: YouTube – ES4TpVsTkgc (English Learning Video)</t>
+          <t>Free education and certified training: YouTube – dLKPBSov2F4 (English Learning Video)</t>
         </is>
       </c>
     </row>
@@ -14797,7 +15902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14882,17 +15987,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Sejda PDF</t>
+          <t>TinyWow</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Online PDF Editor</t>
+          <t>Multi-Tool Suite</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>https://www.sejda.com</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -14902,7 +16007,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Online PDF editor, merge, split, and conversion tools</t>
+          <t>Free online tools for PDF, video, image, and document conversion</t>
         </is>
       </c>
     </row>
@@ -14912,17 +16017,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>tinywow.com</t>
+          <t>Sejda PDF</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Productivity Tool</t>
+          <t>Online PDF Editor</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>https://tinywow.com</t>
+          <t>https://www.sejda.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -14932,7 +16037,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Swiss Army knife of 200+ free online tools for PDF image video and file conversions</t>
+          <t>Online PDF editor, merge, split, and conversion tools</t>
         </is>
       </c>
     </row>
@@ -14946,7 +16051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16116,1052 +17221,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Website Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Website Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Official URL</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>3dtuning.com</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>https://3dtuning.com</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Virtual car customization tool to visualize modifications and dream builds before spending money</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>carcarekiosk.com</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>https://carcarekiosk.com</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Vehicle-specific maintenance video tutorials for your exact car make and model</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>dora.run</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>https://dora.run</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>No-code builder for impressive 3D animated websites without learning WebGL or Three.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>home.by.me</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>https://home.by.me</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>3D home design and room planner to visualize renovations before committing to changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>pacdora.com</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>https://pacdora.com</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>3D packaging mockup generator for product branding with realistic visualization</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Radio Garden</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>https://radio.garden</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Interactive 3D globe allowing users to rotate the earth and tune into live radio stations worldwide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>startmycar.com</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>https://startmycar.com</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Car troubleshooting guide that helps diagnose why your car won't start with solutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>uiverse.io</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>3D Virtual Vehicle Customizer</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>https://uiverse.io</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Community-driven library of free open-source UI elements including buttons cards and loaders</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>jitter.video</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Browser-Based Video Editor</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>https://jitter.video</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Browser-based motion graphics editor for designers who don't want to learn After Effects</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>musclewiki.com</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Browser-Based Video Editor</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>https://musclewiki.com</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Interactive muscle map showing exercises for every body part with video demonstrations</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>whitescreen.online</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Browser-Based Video Editor</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>https://whitescreen.online</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Full-screen color display for testing monitors lighting video calls or cleaning screens</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>clicktheredbutton.com</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Creative Design Platform</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>https://clicktheredbutton.com</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Random weird website discovery tool - click and find something unexpected on the internet</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>dreamforth.com</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Creative Design Platform</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>https://dreamforth.com</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Dream interpretation dictionary to explore what your vivid or recurring dreams might mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>fragrantica.com</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Creative Design Platform</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>https://fragrantica.com</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Comprehensive perfume database with detailed notes and community reviews before you buy</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>music-map.com</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Creative Design Platform</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>https://music-map.com</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Discover similar artists visualized as a spatial map - type any band and explore</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>nullfake.com</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Creative Design Platform</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>https://nullfake.com</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Detect fake Amazon reviews and see adjusted ratings based only on authentic reviews</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>supercook.com</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Creative Design Platform</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>https://supercook.com</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Recipe search engine that finds dishes you can make with ingredients you already have</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>flourish.studio</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>https://flourish.studio</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Create beautiful interactive data visualizations and charts without knowing how to code</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>framer.com</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>https://framer.com</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>No-code website builder with pixel-perfect control for designers who want professional results</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>planyourroom.com</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>https://planyourroom.com</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Drag-and-drop room layout planner to test furniture arrangements before buying or moving</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>pngimg.com</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>https://pngimg.com</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Free database of PNG images with transparent backgrounds ready for design projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>reactbits.dev</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>https://reactbits.dev</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Collection of animated React components ready to copy and paste into your projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>squoosh.app</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>https://squoosh.app</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Google's image compression tool with side-by-side comparison to optimize file sizes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>sweezy-cursors.com</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>https://sweezy-cursors.com</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Custom animated browser cursors with hundreds of themed and animated styles to choose</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>tailornova.com</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>https://tailornova.com</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Generate custom sewing patterns made-to-measure from your exact body measurements</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>thetruesize.com</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>https://thetruesize.com</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Interactive map showing true size of countries by correcting Mercator projection distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>typefaceanimator.com</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>https://typefaceanimator.com</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Browser tool for creating animated typeface transitions and kinetic typography effects</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>uiball.com</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Design Design Platform</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>https://uiball.com</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Free collection of beautiful loading spinners and UI loaders for modern web projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>animejs.com</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>JavaScript Web Animation Engine</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>https://animejs.com</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Lightweight JavaScript animation library for smooth web animations without heavy dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>paperanimator.com</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>JavaScript Web Animation Engine</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>https://paperanimator.com</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Turn hand-drawn character sketches into animations with simple drag-and-drop rigging</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>hyperpost.studio</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Social Media Template Booster</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>https://hyperpost.studio</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Freemium</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Social media template booster packs</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>thetoymaker.com</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Social Media Template Booster</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>https://thetoymaker.com</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Printable paper toy templates you can cut fold and glue into whimsical 3D figures</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/📊 Websites_Master_List.xlsx
+++ b/📊 Websites_Master_List.xlsx
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 3)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Facebook Video Downloader</t>
+          <t>Online downloader for Facebook videos, clips, and private videos.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Facebook Video Downloader</t>
+          <t>Fast online Facebook Video Downloader for MP4 and HD videos.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Instagram Downloader</t>
+          <t>Download Instagram photos, videos, reels, IGTV, and carousels online.</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 2)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Pinterest Video Downloader</t>
+          <t>Fast Pinterest video, GIF, and photo downloader.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Subtitle Automation Tool</t>
+          <t>Automated open-source subtitle generator and downloader tool.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Twitter Video Downloader</t>
+          <t>Direct Twitter (X) video and GIF downloader online.</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Universal Media Downloader</t>
+          <t>Universal media downloader for YouTube, Twitter, Instagram, Reddit with zero ads.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube to MP4 Converter</t>
+          <t>Convert and download YouTube videos to MP4 high-speed online.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx (URL Trick 1)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>YouTube Video , Mp3 download with timestamp</t>
+          <t>YouTube Video &amp; MP3 Timestamp Downloader</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube Video , Mp3 download with timestamp</t>
+          <t>Tool and tutorial to download specific timestamp clips from YouTube videos as MP3 or MP4.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube Video Downloader</t>
+          <t>Online YouTube video downloader for 1080p, 720p, and MP3 audio.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: File Search Engine</t>
+          <t>Open file and media search engine indexing millions of web files.</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Image Processing Tool</t>
+          <t>Online image compressor, resizer, and converter tool.</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Facebook Video Downloader</t>
+          <t>Online downloader for Facebook videos, clips, and private videos.</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Facebook Video Downloader</t>
+          <t>Fast online Facebook Video Downloader for MP4 and HD videos.</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Instagram Downloader</t>
+          <t>Download Instagram photos, videos, reels, IGTV, and carousels online.</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Pinterest Video Downloader</t>
+          <t>Fast Pinterest video, GIF, and photo downloader.</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Subtitle Automation Tool</t>
+          <t>Automated open-source subtitle generator and downloader tool.</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Twitter Video Downloader</t>
+          <t>Direct Twitter (X) video and GIF downloader online.</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Universal Media Downloader</t>
+          <t>Universal media downloader for YouTube, Twitter, Instagram, Reddit with zero ads.</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube to MP4 Converter</t>
+          <t>Convert and download YouTube videos to MP4 high-speed online.</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>YouTube Video , Mp3 download with timestamp</t>
+          <t>YouTube Video &amp; MP3 Timestamp Downloader</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube Video , Mp3 download with timestamp</t>
+          <t>Tool and tutorial to download specific timestamp clips from YouTube videos as MP3 or MP4.</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: YouTube Video Downloader</t>
+          <t>Online YouTube video downloader for 1080p, 720p, and MP3 audio.</t>
         </is>
       </c>
     </row>
@@ -13124,15 +13124,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13143,25 +13144,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Website Name</t>
+          <t>Course / Platform Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Track / Sub-Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Website Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Official URL</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pricing</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -13178,20 +13184,25 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>🧠 Agentic AI &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
           <t>Agentic AI Course</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/a-b-c-of-coding-to-build-ai-agents</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: A B C of Coding to Build AI Agents (Agentic AI Course)</t>
         </is>
@@ -13208,20 +13219,25 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>🧠 Agentic AI &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>Agentic AI Course</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/agentic-ai-design-pattern</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Agentic : AI Design Pattern (Agentic AI Course)</t>
         </is>
@@ -13238,20 +13254,25 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>🧠 Agentic AI &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>Agentic AI Course</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/build-a-resume-review-agentic-system-with-crewai</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Build a Resume Review Agentic System with CrewAI (Agentic AI Course)</t>
         </is>
@@ -13268,20 +13289,25 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>🧠 Agentic AI &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>Agentic AI Course</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/building-agentic-ai-system-with-with-bedrock</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Building Agentic AI System with Bedrock (Agentic AI Course)</t>
         </is>
@@ -13298,20 +13324,25 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>🧠 Agentic AI &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>Agentic AI Course</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/knowledge-bases-and-memory-for-agentic-ai</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Knowledge Bases &amp; Memory for Agentic AI (Agentic AI Course)</t>
         </is>
@@ -13328,20 +13359,25 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>AI Course Platform</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>https://www.elementsofai.com</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Elements of AI (AI Course Platform)</t>
         </is>
@@ -13358,20 +13394,25 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>🔬 Frontier AI Models Deep Dive</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>AI Model Deep Dive Course</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/deep-dive-into-qwq-32b</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Deep Dive Into QwQ-32B (AI Model Deep Dive Course)</t>
         </is>
@@ -13388,20 +13429,25 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>🔬 Frontier AI Models Deep Dive</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>AI Model Deep Dive Course</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/exploring-openai-o3-and-o4-mini</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Exploring OpenAI o3 and o4-mini (AI Model Deep Dive Course)</t>
         </is>
@@ -13418,20 +13464,25 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>🔬 Frontier AI Models Deep Dive</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>AI Model Deep Dive Course</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/getting-started-with-deepseek</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Getting Started with DeepSeek-AI (AI Model Deep Dive Course)</t>
         </is>
@@ -13448,20 +13499,25 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>🔬 Frontier AI Models Deep Dive</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>AI Model Deep Dive Course</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/getting-started-with-openai-o3-mini</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Getting Started with OpenAI o3-mini (AI Model Deep Dive Course)</t>
         </is>
@@ -13478,20 +13534,25 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>🔬 Frontier AI Models Deep Dive</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>AI Model Deep Dive Course</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/xai-grok-3-smartest-ai-on-earth</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: xAI Grok 3: Smartest AI on Earth (AI Model Deep Dive Course)</t>
         </is>
@@ -13508,20 +13569,25 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>AI Training Course</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>https://www.databricks.com/learn/training/generative-ai-fundamentals</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Databricks – Generative AI Fundamentals (AI Training Course)</t>
         </is>
@@ -13538,20 +13604,25 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>☁️ Cloud Computing &amp; Google Skills</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>Cloud Training Path</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>https://www.cloudskillsboost.google/paths/118</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Google Cloud Skills Boost (Cloud Training Path)</t>
         </is>
@@ -13568,20 +13639,25 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>💻 Computer Education &amp; Web Development</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>Computer Courses Platform</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>https://www.stpcomputereducation.com/courses</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: STP Computer Education – Courses (Computer Courses Platform)</t>
         </is>
@@ -13598,20 +13674,25 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>https://chemequations.com</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Auto-balance chemical equations instantly - essential tool for chemistry homework and learning</t>
         </is>
@@ -13628,20 +13709,25 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>https://classcentral.com</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Search engine aggregating online courses from all major platforms with reviews and ratings</t>
         </is>
@@ -13658,20 +13744,25 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>https://cymath.com</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Freemium</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Step-by-step math problem solver that shows you how to get the answer</t>
         </is>
@@ -13688,20 +13779,25 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>https://dungeonscrawl.com</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Freemium</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Create custom dungeon maps online for tabletop RPGs and virtual tabletop sessions</t>
         </is>
@@ -13718,20 +13814,25 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>https://human.biodigital.com</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Interactive 3D human anatomy model for medical students and curious minds to explore</t>
         </is>
@@ -13748,20 +13849,25 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>https://kiddoworksheets.com</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Free printable worksheets for kids covering math reading and educational activities</t>
         </is>
@@ -13778,20 +13884,25 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>https://litsolutions.org</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Free textbook solutions and homework help with step-by-step workings for STEM courses</t>
         </is>
@@ -13808,20 +13919,25 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>https://mindluster.com</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Free online courses with certificates you can add to your resume upon completion</t>
         </is>
@@ -13838,20 +13954,25 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>https://musicca.com</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Interactive music theory lessons with virtual instruments and exercises to practice concepts</t>
         </is>
@@ -13868,20 +13989,25 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>https://phet.colorado.edu</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Free interactive science simulations from University of Colorado for physics chemistry and biology</t>
         </is>
@@ -13898,20 +14024,25 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>https://smart.servier.com</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Free high-resolution medical and scientific images for anatomy biology and healthcare projects</t>
         </is>
@@ -13928,20 +14059,25 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>https://spacetypegenerator.com</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Animated typography effects generator for creating dynamic text for videos and social media</t>
         </is>
@@ -13958,20 +14094,25 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>https://typelit.io</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Freemium</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Practice typing by retyping classic literature - combine skill development with reading great books</t>
         </is>
@@ -13988,20 +14129,25 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>https://typingclub.com</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Freemium</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Structured typing lessons for schools and individuals with gamified progress tracking</t>
         </is>
@@ -14018,20 +14164,25 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>https://wolframalpha.com</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Freemium</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Computational knowledge engine that answers questions with computed data rather than web links</t>
         </is>
@@ -14048,20 +14199,25 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
           <t>Educational Learning Platform</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>https://zty.pe</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Typing game where you shoot down enemy ships by typing words - fun skill practice</t>
         </is>
@@ -14078,20 +14234,25 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
+          <t>🗣️ English &amp; Language Learning</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
           <t>English Learning Page</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>https://www.instagram.com/learn_english_with_shaba</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Instagram – Learn English With Shaba (English Learning Page)</t>
         </is>
@@ -14108,20 +14269,25 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
+          <t>🗣️ English &amp; Language Learning</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
           <t>English Learning Video</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>https://youtu.be/ES4TpVsTkgc</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: YouTube – dLKPBSov2F4 (English Learning Video)</t>
         </is>
@@ -14138,20 +14304,25 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
+          <t>🎁 Free Program Combos &amp; Bundles</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
           <t>Free Program Combo Bundle</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/learning-path/data-science-program</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Data Science Free Program - 9 Courses Combo (Free Program Combo Bundle)</t>
         </is>
@@ -14168,20 +14339,25 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>🎁 Free Program Combos &amp; Bundles</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
           <t>Free Program Combo Bundle</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/learning-path/generative-ai-program-free</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: GenAI Free Program - 7 Courses Combo (Free Program Combo Bundle)</t>
         </is>
@@ -14198,20 +14374,25 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
           <t>Fundamental Tech Course</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/essential-sql-skills-for-data-beginners</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Essential : SQL Skills for Data Beginners (Fundamental Tech Course)</t>
         </is>
@@ -14228,20 +14409,25 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
           <t>Fundamental Tech Course</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/excel-from-beginner-to-expert</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Excel : From Beginner to Expert (Fundamental Tech Course)</t>
         </is>
@@ -14258,20 +14444,25 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
           <t>Fundamental Tech Course</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/genai-landscape</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: GenAI for Everyone (Fundamental Tech Course)</t>
         </is>
@@ -14288,20 +14479,25 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
           <t>Fundamental Tech Course</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/getting-started-with-tableau</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Getting Started with Tableau (Fundamental Tech Course)</t>
         </is>
@@ -14318,20 +14514,25 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
           <t>Fundamental Tech Course</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/introduction-to-data-science</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Introduction to Python (Fundamental Tech Course)</t>
         </is>
@@ -14348,20 +14549,25 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
           <t>Generative AI Course</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/build-product-10x-faster-with-genai</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Build Products 10x Faster with GenAI (Generative AI Course)</t>
         </is>
@@ -14378,20 +14584,25 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
           <t>Generative AI Course</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/deepseek-from-scratch</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: DeepSeek from Scratch (Generative AI Course)</t>
         </is>
@@ -14408,20 +14619,25 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
           <t>Generative AI Course</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/genai-applied-to-quantitative-finance-for-control-implementation</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: GenAI for Quantitative Finance &amp; Control Implementation (Generative AI Course)</t>
         </is>
@@ -14438,20 +14654,25 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
           <t>Generative AI Course</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/genai-a-way-of-life</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Generative AI - A Way of Life (Generative AI Course)</t>
         </is>
@@ -14468,20 +14689,25 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
           <t>Generative AI Course</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/reimagining-genai-common-mistakes-and-best-practices-for-success</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Reimagining GenAI: Common Mistakes and Best Practices for Success (Generative AI Course)</t>
         </is>
@@ -14498,20 +14724,25 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/a-complete-mlops-journey</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: A Complete MLops Journey (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14528,20 +14759,25 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/a-comprehensive-learning-path-to-become-a-data-scientist-in-twenty-twenty-four</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: A Comprehensive Learning Path to Become a Data Scientist in 2025 (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14558,20 +14794,25 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/bagging-boosting-ML-Algorithms</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Bagging and Boosting ML Algorithms (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14588,20 +14829,25 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/free-building-textclassification-natural-language-processing</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Building Text Classification Models in NLP (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14618,20 +14864,25 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/dimensionality-reduction-for-machine-learning</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Dimensionality Reduction for Machine Learning (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14648,20 +14899,25 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/ensemble-learning-and-ensemble-learning-techniques</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Ensemble Learning and Ensemble Learning Techniques (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14678,20 +14934,25 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/Fundamentals-of-Regression-Analysis</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Fundamentals of Regression Analysis (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14708,20 +14969,25 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/getting-started-with-deep-learning</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Getting Started with Deep Learning (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14738,20 +15004,25 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/getting-started-with-llms</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Getting Started With Large Language Models (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14768,20 +15039,25 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/introduction-to-ai-ml</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Introduction to AI &amp; ML (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14798,20 +15074,25 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/introduction-to-transformers-and-attention-mechanisms</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Introduction to Transformers and Attention Mechanisms (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14828,20 +15109,25 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/K-Nearest-Neighbors-KNN-Algorithm</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: K-Nearest Neighbors (KNN) Algorithm in Python and R (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14858,20 +15144,25 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/machine-learning-certification-program-beginners</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Machine Learning Certification course for Beginners (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14888,20 +15179,25 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/naive-bayes</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Naive Bayes from Scratch (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14918,20 +15214,25 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/free-unsupervised-ml-guide</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: The A to Z of Unsupervised ML (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14948,20 +15249,25 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/free-understanding-linear-regression</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Understanding Linear Regression (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -14978,20 +15284,25 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
           <t>Machine Learning &amp; Deep Learning Course</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/understanding-the-working-of-neural-networks</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Understanding the working of Neural Networks (Machine Learning &amp; Deep Learning Course)</t>
         </is>
@@ -15008,20 +15319,25 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
+          <t>☁️ Cloud Computing &amp; Google Skills</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
           <t>Official Google Training</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>https://skillshop.withgoogle.com</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Google Skillshop (Official Google Training)</t>
         </is>
@@ -15038,20 +15354,25 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
           <t>Online Course</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>https://www.coursera.org/learn/generative-ai-for-everyone</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Coursera – Generative AI for Everyone (Online Course)</t>
         </is>
@@ -15068,20 +15389,25 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
           <t>Online Course</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>https://www.coursera.org/learn/generative-ai-with-llms</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Coursera – Generative AI with LLMs (Online Course)</t>
         </is>
@@ -15098,20 +15424,25 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
+          <t>📊 Machine Learning &amp; Deep Learning Mastery</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
           <t>Online Course</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>https://www.coursera.org/learn/machine-learning</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Coursera – Machine Learning (Online Course)</t>
         </is>
@@ -15128,20 +15459,25 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
           <t>Online Course Platform</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>https://www.mygreatlearning.com/academy</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Great Learning Academy (Online Course Platform)</t>
         </is>
@@ -15158,20 +15494,25 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
+          <t>🤖 Generative AI &amp; LLM Engineering</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
           <t>Open Source AI Course</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>https://github.com/microsoft/generative-ai-for-beginners</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: GitHub – Microsoft Generative AI for Beginners (Open Source AI Course)</t>
         </is>
@@ -15188,20 +15529,25 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
+          <t>📈 Data Analytics, SQL &amp; Fundamental Tech</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
           <t>Professional Certificate</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>https://www.coursera.org/professional-certificates/google-data-analytics</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: Coursera – Google Data Analytics (Professional Certificate)</t>
         </is>
@@ -15218,20 +15564,25 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/big-mart-sales-prediction-using-r</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Big Mart Sales Prediction Using R (Project-Based Learning Course)</t>
         </is>
@@ -15248,20 +15599,25 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/build-data-pipelines-with-apache-airflow</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Build Data Pipelines with Apache Airflow (Project-Based Learning Course)</t>
         </is>
@@ -15278,20 +15634,25 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/building-a-deep-research-ai-agent</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Building a Deep Research AI Agent (Project-Based Learning Course)</t>
         </is>
@@ -15308,20 +15669,25 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/coding-a-chatgpt-style-language-model-from-scratch-in-pytorch</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Coding a ChatGPT-style Language Model From Scratch in Pytorch (Project-Based Learning Course)</t>
         </is>
@@ -15338,20 +15704,25 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/how-to-build-an-image-generator-web-app-with-zero-coding</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: How to Build an Image Generator Web App with Zero Coding (Project-Based Learning Course)</t>
         </is>
@@ -15368,20 +15739,25 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/loan-prediction-practice-problem-using-python</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Loan Prediction Practice Problem (Using Python) (Project-Based Learning Course)</t>
         </is>
@@ -15398,20 +15774,25 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/model-deployment-using-fastapi</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Model Deployment using FastAPI (Project-Based Learning Course)</t>
         </is>
@@ -15428,20 +15809,25 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
+          <t>🛠️ Project-Based AI &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
           <t>Project-Based Learning Course</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/openengage-a-complete-ai-driven-marketing-engine</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: OpenEngage: Build a complete AI Driven Marketing Engine (Project-Based Learning Course)</t>
         </is>
@@ -15458,20 +15844,25 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
+          <t>🔗 RAG (Retrieval-Augmented Generation)</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
           <t>RAG Application Course</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/build-a-document-retriever-search-engine-with-langchain</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Build a Document Retriever Search Engine with LangChain (RAG Application Course)</t>
         </is>
@@ -15488,20 +15879,25 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
+          <t>🔗 RAG (Retrieval-Augmented Generation)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
           <t>RAG Application Course</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/building-first-rag-systems-using-llamaindex</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Build your first RAG system using Llamaindex (RAG Application Course)</t>
         </is>
@@ -15518,20 +15914,25 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
+          <t>🔗 RAG (Retrieval-Augmented Generation)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
           <t>RAG Application Course</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/end-to-end-app-rag-application-development-with-langchain-and-streamlit</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: End to end RAG Application Development with LangChain and Streamlit (RAG Application Course)</t>
         </is>
@@ -15548,20 +15949,25 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
+          <t>🔗 RAG (Retrieval-Augmented Generation)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
           <t>RAG Application Course</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/improving-real-world-rag-systems-key-challenges</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Improving Real World RAG Systems :Key Challenges (RAG Application Course)</t>
         </is>
@@ -15578,20 +15984,25 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
+          <t>🔗 RAG (Retrieval-Augmented Generation)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
           <t>RAG Application Course</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/mastering-multimodal-rag-and-embeddings-with-amazon-nova-and-bedrock</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Mastering Multimodal RAG &amp; Embeddings with Amazon Nova &amp; Bedrock (RAG Application Course)</t>
         </is>
@@ -15608,20 +16019,25 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
+          <t>🌐 Academic STEM Tools &amp; Learning Platforms</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
           <t>Skill Development Platform</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>https://www.learnvern.com</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: LearnVern (Skill Development Platform)</t>
         </is>
@@ -15638,20 +16054,25 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
+          <t>💻 Computer Education &amp; Web Development</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
           <t>Study Notes / Learning Material</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>https://www.stpcomputereducation.com/notes</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: STP Computer Education – Notes (Study Notes / Learning Material)</t>
         </is>
@@ -15668,20 +16089,25 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
+          <t>⚡ Vibe Coding &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
           <t>Vibe Coding Course</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/building-a-customized-newsletter-ai-agent</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Building a Customized Newsletter AI Agent (Vibe Coding Course)</t>
         </is>
@@ -15698,20 +16124,25 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
+          <t>⚡ Vibe Coding &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
           <t>Vibe Coding Course</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/guide-to-vibe-coding-in-windsurf</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Guide to Vibe Coding in Windsurf (Vibe Coding Course)</t>
         </is>
@@ -15728,20 +16159,25 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
+          <t>⚡ Vibe Coding &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
           <t>Vibe Coding Course</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/n8n-a-complete-guide-to-the-automation-tool</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: n8n - A Complete Guide to Automation Tool (Vibe Coding Course)</t>
         </is>
@@ -15758,20 +16194,25 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
+          <t>⚡ Vibe Coding &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
           <t>Vibe Coding Course</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>https://www.analyticsvidhya.com/courses/vibe-coding-with-replit</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>Comprehensive free training course: Vibe Coding with Replit (Vibe Coding Course)</t>
         </is>
@@ -15788,20 +16229,25 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
+          <t>💻 Computer Education &amp; Web Development</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
           <t>Web Development Course</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>https://www.stpcomputereducation.com/courses/web-development.html</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Free + Paid</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Free education and certified training: STP Computer Education – Web Development (Web Development Course)</t>
         </is>
@@ -15809,94 +16255,94 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16366,7 +16812,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: File Search Engine</t>
+          <t>Open file and media search engine indexing millions of web files.</t>
         </is>
       </c>
     </row>
@@ -16486,7 +16932,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>High-speed online tool: Image Processing Tool</t>
+          <t>Online image compressor, resizer, and converter tool.</t>
         </is>
       </c>
     </row>

--- a/📊 Websites_Master_List.xlsx
+++ b/📊 Websites_Master_List.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>HTML Visuals</t>
+          <t>Explorer.globe.engineer</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>https://www.htmlvisuals.com</t>
+          <t>https://explorer.globe.engineer</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: HTML Visuals (Web Development Resource)</t>
+          <t>High-utility developer platform: Explorer.globe.engineer (Web Development Resource)</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>HTML.com</t>
+          <t>HTML Visuals</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>https://html.com</t>
+          <t>https://www.htmlvisuals.com</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: HTML.com (Web Development Resource)</t>
+          <t>High-utility developer platform: HTML Visuals (Web Development Resource)</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Programming &amp; Tech Learning Res)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Web Development Resources - BH)</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>HTML5 Cheat Sheet</t>
+          <t>HTML.com</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>https://www.geeksforgeeks.org/html5-cheat-sheet</t>
+          <t>https://html.com</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: HTML5 Cheat Sheet (Web Development Resource)</t>
+          <t>High-utility developer platform: HTML.com (Web Development Resource)</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Web Development Resources - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Programming &amp; Tech Learning Res)</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>LearnWeb3</t>
+          <t>HTML5 Cheat Sheet</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>https://learnweb3.io</t>
+          <t>https://www.geeksforgeeks.org/html5-cheat-sheet</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: LearnWeb3 (Web Development Resource)</t>
+          <t>High-utility developer platform: HTML5 Cheat Sheet (Web Development Resource)</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Programming &amp; Tech Learning Res)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Web Development Resources - BH)</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>W3Schools</t>
+          <t>LearnWeb3</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>https://www.w3schools.com</t>
+          <t>https://learnweb3.io</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: W3Schools (Web Development Resource)</t>
+          <t>High-utility developer platform: LearnWeb3 (Web Development Resource)</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Web Development Resources - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Programming &amp; Tech Learning Res)</t>
         </is>
       </c>
     </row>
@@ -11975,12 +11975,12 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Academind</t>
+          <t>W3Schools</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>YouTube Coding Channel</t>
+          <t>Web Development Resource</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@academind</t>
+          <t>https://www.w3schools.com</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>Deep-dive technical tutorials on React, Angular, Vue, Node.js, and cloud tech.</t>
+          <t>High-utility developer platform: W3Schools (Web Development Resource)</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Web Development Resources - BH)</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Academind</t>
+          <t>https://www.youtube.com/@academind</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>Developer platform: Academind (YouTube Coding Channel)</t>
+          <t>Deep-dive technical tutorials on React, Angular, Vue, Node.js, and cloud tech.</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Sheet32 - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Anuj Bhaiya</t>
+          <t>Academind</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AnujBhaiya</t>
+          <t>https://www.youtube.com/@Academind</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>Data structures, algorithms, system design, and software engineering placement prep.</t>
+          <t>Developer platform: Academind (YouTube Coding Channel)</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Sheet32 - BH)</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Apni Kaksha</t>
+          <t>Anuj Bhaiya</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ApniKaksha</t>
+          <t>https://www.youtube.com/@AnujBhaiya</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>Free quality coding education, college roadmap, and placement interview guidance.</t>
+          <t>Data structures, algorithms, system design, and software engineering placement prep.</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Bhagwan Singh Vishwakarma</t>
+          <t>Apni Kaksha</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@bhagwansinghvishwakarma</t>
+          <t>https://www.youtube.com/@ApniKaksha</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
-          <t>Computer science, programming, and technical academic tutorials.</t>
+          <t>Free quality coding education, college roadmap, and placement interview guidance.</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Clever Programmer</t>
+          <t>Bhagwan Singh Vishwakarma</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CleverProgrammer</t>
+          <t>https://www.youtube.com/@bhagwansinghvishwakarma</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
-          <t>Full-stack web development clone builds with JavaScript, React, and Python.</t>
+          <t>Computer science, programming, and technical academic tutorials.</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>CodeWithHarry</t>
+          <t>Clever Programmer</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CodeWithHarry</t>
+          <t>https://www.youtube.com/@CleverProgrammer</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>Top Indian programming channel teaching Python, Web Dev, C, C++, and Java in Hindi.</t>
+          <t>Full-stack web development clone builds with JavaScript, React, and Python.</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Derek Banas</t>
+          <t>CodeWithHarry</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@derekbanas</t>
+          <t>https://www.youtube.com/@CodeWithHarry</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
-          <t>Learn complex programming languages and frameworks in single comprehensive videos.</t>
+          <t>Top Indian programming channel teaching Python, Web Dev, C, C++, and Java in Hindi.</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>freeCodeCamp.org</t>
+          <t>Derek Banas</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@freecodecamp</t>
+          <t>https://www.youtube.com/@derekbanas</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>Thousands of hours of free coding courses from industry professionals.</t>
+          <t>Learn complex programming languages and frameworks in single comprehensive videos.</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Gate Smashers</t>
+          <t>freeCodeCamp.org</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GateSmashers</t>
+          <t>https://www.youtube.com/@freecodecamp</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>Operating systems, DBMS, computer networks, and GATE computer science lectures.</t>
+          <t>Thousands of hours of free coding courses from industry professionals.</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Jenny's Lectures CS IT</t>
+          <t>Gate Smashers</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@JennyslecturesCSIT</t>
+          <t>https://www.youtube.com/@GateSmashers</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>Engineering CS/IT subjects, algorithms, data structures, and theory of computation.</t>
+          <t>Operating systems, DBMS, computer networks, and GATE computer science lectures.</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>LearnCode.academy</t>
+          <t>Jenny's Lectures CS IT</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@learncodeacademy</t>
+          <t>https://www.youtube.com/@JennyslecturesCSIT</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>Web development tutorials, responsive design, JavaScript, React, and DevOps.</t>
+          <t>Engineering CS/IT subjects, algorithms, data structures, and theory of computation.</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>mycodeschool</t>
+          <t>LearnCode.academy</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@mycodeschool</t>
+          <t>https://www.youtube.com/@learncodeacademy</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>Classic, world-renowned lessons on data structures, pointers, and memory management.</t>
+          <t>Web development tutorials, responsive design, JavaScript, React, and DevOps.</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>MySirG.com</t>
+          <t>mycodeschool</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MySirG</t>
+          <t>https://www.youtube.com/@mycodeschool</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>Premier Hindi channel for C, C++, Python, Data Structures, and programming fundamentals.</t>
+          <t>Classic, world-renowned lessons on data structures, pointers, and memory management.</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Programming Hub</t>
+          <t>MySirG.com</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProgrammingHub</t>
+          <t>https://www.youtube.com/@MySirG</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>Accessible tech tutorials covering AI, app development, and programming languages.</t>
+          <t>Premier Hindi channel for C, C++, Python, Data Structures, and programming fundamentals.</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Programming with Mosh</t>
+          <t>Programming Hub</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@programmingwithmosh</t>
+          <t>https://www.youtube.com/@ProgrammingHub</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>Clear, concise tutorials on Python, JavaScript, React, C#, and SQL.</t>
+          <t>Accessible tech tutorials covering AI, app development, and programming languages.</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProgrammingwithMosh</t>
+          <t>https://www.youtube.com/@programmingwithmosh</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>Developer platform: Programming with Mosh (YouTube Coding Channel)</t>
+          <t>Clear, concise tutorials on Python, JavaScript, React, C#, and SQL.</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Sheet32 - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>ProgrammingKnowledge</t>
+          <t>Programming with Mosh</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProgrammingKnowledge</t>
+          <t>https://www.youtube.com/@ProgrammingwithMosh</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>Step-by-step programming tutorials on Android, Java, Python, and Linux.</t>
+          <t>Developer platform: Programming with Mosh (YouTube Coding Channel)</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Sheet32 - BH)</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>SoloLearn</t>
+          <t>ProgrammingKnowledge</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SoloLearn</t>
+          <t>https://www.youtube.com/@ProgrammingKnowledge</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>Bite-sized mobile-first coding lessons and language deep-dives.</t>
+          <t>Step-by-step programming tutorials on Android, Java, Python, and Linux.</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>SortedCoding</t>
+          <t>SoloLearn</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SortedCoding</t>
+          <t>https://www.youtube.com/@SoloLearn</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>Frontend tricks, CSS animations, JavaScript projects, and coding shorts.</t>
+          <t>Bite-sized mobile-first coding lessons and language deep-dives.</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>https://youtube.com/@sortedcoding?si=OViA9rO2lCUgosxT</t>
+          <t>https://www.youtube.com/@SortedCoding</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>Developer platform: SortedCoding (YouTube Coding Channel)</t>
+          <t>Frontend tricks, CSS animations, JavaScript projects, and coding shorts.</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Sheet32 - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>Telusko</t>
+          <t>SortedCoding</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Telusko</t>
+          <t>https://youtube.com/@sortedcoding?si=OViA9rO2lCUgosxT</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>Java, Python, Blockchain, Docker, and full-stack web development tutorials.</t>
+          <t>Developer platform: SortedCoding (YouTube Coding Channel)</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Sheet32 - BH)</t>
         </is>
       </c>
     </row>
@@ -12855,7 +12855,7 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>thenewboston</t>
+          <t>Telusko</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@thenewboston</t>
+          <t>https://www.youtube.com/@Telusko</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>Pioneering computer science, web dev, and blockchain video tutorials.</t>
+          <t>Java, Python, Blockchain, Docker, and full-stack web development tutorials.</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>Traversy Media</t>
+          <t>thenewboston</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TraversyMedia</t>
+          <t>https://www.youtube.com/@thenewboston</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>Practical web development tutorials, crash courses, and project builds.</t>
+          <t>Pioneering computer science, web dev, and blockchain video tutorials.</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -12935,37 +12935,37 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>heyzxz.me</t>
+          <t>Traversy Media</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>AI Audio &amp; Voice Tool</t>
+          <t>YouTube Coding Channel</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
+          <t>💻 Coding &amp; Developer Platforms</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>https://heyzxz.me</t>
+          <t>https://www.youtube.com/@TraversyMedia</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>AI voice synthesis and cloning for content creators needing voiceovers without recording</t>
+          <t>Practical web development tutorials, crash courses, and project builds.</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 💻 Coding Websites.xlsx (Y-I-T - BH)</t>
         </is>
       </c>
     </row>
@@ -12975,12 +12975,12 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>freepik.com</t>
+          <t>heyzxz.me</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>AI Image Generator &amp; Enhancer</t>
+          <t>AI Audio &amp; Voice Tool</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>https://freepik.com</t>
+          <t>https://heyzxz.me</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>Stock graphics library with AI image generation tools - one-stop shop for visual assets</t>
+          <t>AI voice synthesis and cloning for content creators needing voiceovers without recording</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>meshy.ai</t>
+          <t>freepik.com</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>https://meshy.ai</t>
+          <t>https://freepik.com</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>AI generates 3D models from text prompts or images for games and visualization</t>
+          <t>Stock graphics library with AI image generation tools - one-stop shop for visual assets</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>newarc.ai</t>
+          <t>meshy.ai</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>https://newarc.ai</t>
+          <t>https://meshy.ai</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>AI architecture design tool that generates photorealistic building visualizations from concepts</t>
+          <t>AI generates 3D models from text prompts or images for games and visualization</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>reimaginehome.ai</t>
+          <t>newarc.ai</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>https://reimaginehome.ai</t>
+          <t>https://newarc.ai</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>Upload a room photo and get AI-generated interior design ideas in different styles</t>
+          <t>AI architecture design tool that generates photorealistic building visualizations from concepts</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>remove.photos</t>
+          <t>reimaginehome.ai</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>https://remove.photos</t>
+          <t>https://reimaginehome.ai</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>AI background remover for quick photo editing in your browser - no software needed</t>
+          <t>Upload a room photo and get AI-generated interior design ideas in different styles</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -13175,12 +13175,12 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>autodraw.com</t>
+          <t>remove.photos</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>AI Productivity &amp; Generation Tool</t>
+          <t>AI Image Generator &amp; Enhancer</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -13190,17 +13190,17 @@
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
-          <t>https://autodraw.com</t>
+          <t>https://remove.photos</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>Google's AI that turns rough sketches into clean professional drawings instantly</t>
+          <t>AI background remover for quick photo editing in your browser - no software needed</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>chef.convex.dev</t>
+          <t>autodraw.com</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
@@ -13230,17 +13230,17 @@
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>https://chef.convex.dev</t>
+          <t>https://autodraw.com</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>AI generates real-time app backends from prompts - deploy working prototypes in minutes</t>
+          <t>Google's AI that turns rough sketches into clean professional drawings instantly</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>chefgpt.xyz</t>
+          <t>chef.convex.dev</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
@@ -13270,17 +13270,17 @@
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>https://chefgpt.xyz</t>
+          <t>https://chef.convex.dev</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>AI suggests recipes based on ingredients already in your fridge to reduce food waste</t>
+          <t>AI generates real-time app backends from prompts - deploy working prototypes in minutes</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>collov.ai</t>
+          <t>chefgpt.xyz</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
@@ -13310,17 +13310,17 @@
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>https://collov.ai</t>
+          <t>https://chefgpt.xyz</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>AI virtual home staging that transforms empty rooms into furnished spaces for listings</t>
+          <t>AI suggests recipes based on ingredients already in your fridge to reduce food waste</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>coze.com</t>
+          <t>collov.ai</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>https://coze.com</t>
+          <t>https://collov.ai</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>Build custom AI chatbots and agents without code - deploy to messaging platforms</t>
+          <t>AI virtual home staging that transforms empty rooms into furnished spaces for listings</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>flowith.io</t>
+          <t>coze.com</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>https://flowith.io</t>
+          <t>https://coze.com</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>AI workspace with infinite canvas for non-linear conversations and complex reasoning tasks</t>
+          <t>Build custom AI chatbots and agents without code - deploy to messaging platforms</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>gptexcel.uk</t>
+          <t>flowith.io</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
-          <t>https://gptexcel.uk</t>
+          <t>https://flowith.io</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>AI generates spreadsheet formulas from plain English - stop memorizing VLOOKUP syntax</t>
+          <t>AI workspace with infinite canvas for non-linear conversations and complex reasoning tasks</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>kittl.com</t>
+          <t>gptexcel.uk</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>https://kittl.com</t>
+          <t>https://gptexcel.uk</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>AI-powered design tool perfect for print-on-demand sellers creating professional graphics quickly</t>
+          <t>AI generates spreadsheet formulas from plain English - stop memorizing VLOOKUP syntax</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>layla.ai</t>
+          <t>kittl.com</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="E326" s="5" t="inlineStr">
         <is>
-          <t>https://layla.ai</t>
+          <t>https://kittl.com</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
-          <t>AI travel itinerary planner that creates balanced trip plans from your preferences</t>
+          <t>AI-powered design tool perfect for print-on-demand sellers creating professional graphics quickly</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>natively.dev</t>
+          <t>layla.ai</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>https://natively.dev</t>
+          <t>https://layla.ai</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>AI no-code platform for building native mobile apps without any programming knowledge</t>
+          <t>AI travel itinerary planner that creates balanced trip plans from your preferences</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>same.new</t>
+          <t>natively.dev</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="E328" s="5" t="inlineStr">
         <is>
-          <t>https://same.new</t>
+          <t>https://natively.dev</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>AI clones any website's design in seconds and generates the code for you</t>
+          <t>AI no-code platform for building native mobile apps without any programming knowledge</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>sketch.metademolab.com</t>
+          <t>same.new</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
@@ -13630,17 +13630,17 @@
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>https://sketch.metademolab.com</t>
+          <t>https://same.new</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>Meta's AI that automatically animates hand-drawn character sketches - free research demo</t>
+          <t>AI clones any website's design in seconds and generates the code for you</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -13655,12 +13655,12 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>intangible.ai</t>
+          <t>sketch.metademolab.com</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>AI Video Generation &amp; Pre-Production</t>
+          <t>AI Productivity &amp; Generation Tool</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -13670,17 +13670,17 @@
       </c>
       <c r="E330" s="5" t="inlineStr">
         <is>
-          <t>https://intangible.ai</t>
+          <t>https://sketch.metademolab.com</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>AI video generation for pre-production visualization - save thousands on production costs</t>
+          <t>Meta's AI that automatically animates hand-drawn character sketches - free research demo</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>app.emergent.sh</t>
+          <t>intangible.ai</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>AI Writing &amp; Copywriting Assistant</t>
+          <t>AI Video Generation &amp; Pre-Production</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>https://app.emergent.sh</t>
+          <t>https://intangible.ai</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>AI builds functional web app MVPs from text prompts - great for rapid prototyping</t>
+          <t>AI video generation for pre-production visualization - save thousands on production costs</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>enzostvs-deepsite.hf.space</t>
+          <t>app.emergent.sh</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
@@ -13750,17 +13750,17 @@
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>https://enzostvs-deepsite.hf.space</t>
+          <t>https://app.emergent.sh</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>AI generates complete websites from text prompts using open-source models - free hosting included</t>
+          <t>AI builds functional web app MVPs from text prompts - great for rapid prototyping</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>gamma.app</t>
+          <t>enzostvs-deepsite.hf.space</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
@@ -13790,17 +13790,17 @@
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>https://gamma.app</t>
+          <t>https://enzostvs-deepsite.hf.space</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G333" s="4" t="inlineStr">
         <is>
-          <t>AI generates complete presentations from text - turn ideas into slides in minutes</t>
+          <t>AI generates complete websites from text prompts using open-source models - free hosting included</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>napkin.ai</t>
+          <t>gamma.app</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>https://napkin.ai</t>
+          <t>https://gamma.app</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="G334" s="4" t="inlineStr">
         <is>
-          <t>AI transforms text into visual diagrams and illustrations automatically - just paste and go</t>
+          <t>AI generates complete presentations from text - turn ideas into slides in minutes</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>ponder.chat</t>
+          <t>napkin.ai</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>https://ponder.chat</t>
+          <t>https://napkin.ai</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G335" s="4" t="inlineStr">
         <is>
-          <t>AI writing assistant for creating blog posts social media content and marketing copy</t>
+          <t>AI transforms text into visual diagrams and illustrations automatically - just paste and go</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>text-to-cad.zoo.dev</t>
+          <t>ponder.chat</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
@@ -13910,17 +13910,17 @@
       </c>
       <c r="E336" s="5" t="inlineStr">
         <is>
-          <t>https://text-to-cad.zoo.dev</t>
+          <t>https://ponder.chat</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
-          <t>AI generates 3D CAD models from text descriptions for engineering and design projects</t>
+          <t>AI writing assistant for creating blog posts social media content and marketing copy</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -13935,22 +13935,22 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>chemequations.com</t>
+          <t>text-to-cad.zoo.dev</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Educational Learning Platform</t>
+          <t>AI Writing &amp; Copywriting Assistant</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>🎓 Free Courses &amp; Learning Platforms</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>https://chemequations.com</t>
+          <t>https://text-to-cad.zoo.dev</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G337" s="4" t="inlineStr">
         <is>
-          <t>Auto-balance chemical equations instantly - essential tool for chemistry homework and learning</t>
+          <t>AI generates 3D CAD models from text descriptions for engineering and design projects</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>cymath.com</t>
+          <t>chemequations.com</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="E338" s="5" t="inlineStr">
         <is>
-          <t>https://cymath.com</t>
+          <t>https://chemequations.com</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
         <is>
-          <t>Step-by-step math problem solver that shows you how to get the answer</t>
+          <t>Auto-balance chemical equations instantly - essential tool for chemistry homework and learning</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>dungeonscrawl.com</t>
+          <t>cymath.com</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>https://dungeonscrawl.com</t>
+          <t>https://cymath.com</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G339" s="4" t="inlineStr">
         <is>
-          <t>Create custom dungeon maps online for tabletop RPGs and virtual tabletop sessions</t>
+          <t>Step-by-step math problem solver that shows you how to get the answer</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>human.biodigital.com</t>
+          <t>dungeonscrawl.com</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
@@ -14070,17 +14070,17 @@
       </c>
       <c r="E340" s="5" t="inlineStr">
         <is>
-          <t>https://human.biodigital.com</t>
+          <t>https://dungeonscrawl.com</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
         <is>
-          <t>Interactive 3D human anatomy model for medical students and curious minds to explore</t>
+          <t>Create custom dungeon maps online for tabletop RPGs and virtual tabletop sessions</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>kiddoworksheets.com</t>
+          <t>human.biodigital.com</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>https://kiddoworksheets.com</t>
+          <t>https://human.biodigital.com</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="G341" s="4" t="inlineStr">
         <is>
-          <t>Free printable worksheets for kids covering math reading and educational activities</t>
+          <t>Interactive 3D human anatomy model for medical students and curious minds to explore</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>litsolutions.org</t>
+          <t>kiddoworksheets.com</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E342" s="5" t="inlineStr">
         <is>
-          <t>https://litsolutions.org</t>
+          <t>https://kiddoworksheets.com</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="G342" s="4" t="inlineStr">
         <is>
-          <t>Free textbook solutions and homework help with step-by-step workings for STEM courses</t>
+          <t>Free printable worksheets for kids covering math reading and educational activities</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>mindluster.com</t>
+          <t>litsolutions.org</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>https://mindluster.com</t>
+          <t>https://litsolutions.org</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="G343" s="4" t="inlineStr">
         <is>
-          <t>Free online courses with certificates you can add to your resume upon completion</t>
+          <t>Free textbook solutions and homework help with step-by-step workings for STEM courses</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>musicca.com</t>
+          <t>mindluster.com</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="E344" s="5" t="inlineStr">
         <is>
-          <t>https://musicca.com</t>
+          <t>https://mindluster.com</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="G344" s="4" t="inlineStr">
         <is>
-          <t>Interactive music theory lessons with virtual instruments and exercises to practice concepts</t>
+          <t>Free online courses with certificates you can add to your resume upon completion</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>phet.colorado.edu</t>
+          <t>musicca.com</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>https://phet.colorado.edu</t>
+          <t>https://musicca.com</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="G345" s="4" t="inlineStr">
         <is>
-          <t>Free interactive science simulations from University of Colorado for physics chemistry and biology</t>
+          <t>Interactive music theory lessons with virtual instruments and exercises to practice concepts</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>smart.servier.com</t>
+          <t>phet.colorado.edu</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="E346" s="5" t="inlineStr">
         <is>
-          <t>https://smart.servier.com</t>
+          <t>https://phet.colorado.edu</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="G346" s="4" t="inlineStr">
         <is>
-          <t>Free high-resolution medical and scientific images for anatomy biology and healthcare projects</t>
+          <t>Free interactive science simulations from University of Colorado for physics chemistry and biology</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>spacetypegenerator.com</t>
+          <t>smart.servier.com</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>https://spacetypegenerator.com</t>
+          <t>https://smart.servier.com</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="G347" s="4" t="inlineStr">
         <is>
-          <t>Animated typography effects generator for creating dynamic text for videos and social media</t>
+          <t>Free high-resolution medical and scientific images for anatomy biology and healthcare projects</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>typelit.io</t>
+          <t>spacetypegenerator.com</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="E348" s="5" t="inlineStr">
         <is>
-          <t>https://typelit.io</t>
+          <t>https://spacetypegenerator.com</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
         <is>
-          <t>Practice typing by retyping classic literature - combine skill development with reading great books</t>
+          <t>Animated typography effects generator for creating dynamic text for videos and social media</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>typingclub.com</t>
+          <t>typelit.io</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>https://typingclub.com</t>
+          <t>https://typelit.io</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="G349" s="4" t="inlineStr">
         <is>
-          <t>Structured typing lessons for schools and individuals with gamified progress tracking</t>
+          <t>Practice typing by retyping classic literature - combine skill development with reading great books</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>wolframalpha.com</t>
+          <t>typingclub.com</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="E350" s="5" t="inlineStr">
         <is>
-          <t>https://wolframalpha.com</t>
+          <t>https://typingclub.com</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G350" s="4" t="inlineStr">
         <is>
-          <t>Computational knowledge engine that answers questions with computed data rather than web links</t>
+          <t>Structured typing lessons for schools and individuals with gamified progress tracking</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>zty.pe</t>
+          <t>wolframalpha.com</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
@@ -14510,17 +14510,17 @@
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>https://zty.pe</t>
+          <t>https://wolframalpha.com</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
         <is>
-          <t>Typing game where you shoot down enemy ships by typing words - fun skill practice</t>
+          <t>Computational knowledge engine that answers questions with computed data rather than web links</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -14535,22 +14535,22 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>PDF Chef (Mobile)</t>
+          <t>zty.pe</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Mobile PDF Tool</t>
+          <t>Educational Learning Platform</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>📄 PDF &amp; Document Utilities</t>
+          <t>🎓 Free Courses &amp; Learning Platforms</t>
         </is>
       </c>
       <c r="E352" s="5" t="inlineStr">
         <is>
-          <t>https://play.google.com/store/apps/details?id=com.dhananjaytech.pdfchef</t>
+          <t>https://zty.pe</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="G352" s="4" t="inlineStr">
         <is>
-          <t>Offline PDF management and conversion app</t>
+          <t>Typing game where you shoot down enemy ships by typing words - fun skill practice</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr">
         <is>
-          <t>Excel: 📄 PDF Resources.xlsx</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>TinyWow</t>
+          <t>PDF Chef (Mobile)</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Multi-Tool Suite</t>
+          <t>Mobile PDF Tool</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -14590,22 +14590,22 @@
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>https://tinywow.com</t>
+          <t>https://play.google.com/store/apps/details?id=com.dhananjaytech.pdfchef</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
         <is>
-          <t>Free online tools for PDF, video, image, and document conversion</t>
+          <t>Offline PDF management and conversion app</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 📄 PDF Resources.xlsx</t>
         </is>
       </c>
     </row>
@@ -14615,12 +14615,12 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Sejda PDF</t>
+          <t>TinyWow</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Online PDF Editor</t>
+          <t>Multi-Tool Suite</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>https://www.sejda.com</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="G354" s="4" t="inlineStr">
         <is>
-          <t>Online PDF editor, merge, split, and conversion tools</t>
+          <t>Free online tools for PDF, video, image, and document conversion</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>Excel: 📄 PDF Resources.xlsx</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -14655,22 +14655,22 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>coddy.tech</t>
+          <t>Sejda PDF</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Developer &amp; Code Utility</t>
+          <t>Online PDF Editor</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Web Utilities &amp; Productivity</t>
+          <t>📄 PDF &amp; Document Utilities</t>
         </is>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>https://coddy.tech</t>
+          <t>https://www.sejda.com</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="G355" s="4" t="inlineStr">
         <is>
-          <t>Bite-sized coding lessons you complete in your browser with instant feedback</t>
+          <t>Online PDF editor, merge, split, and conversion tools</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 📄 PDF Resources.xlsx</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>internet-janitor.itch.io</t>
+          <t>coddy.tech</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
@@ -14710,17 +14710,17 @@
       </c>
       <c r="E356" s="5" t="inlineStr">
         <is>
-          <t>https://internet-janitor.itch.io</t>
+          <t>https://coddy.tech</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
         <is>
-          <t>Tool for making interactive fiction and clicky experiences without learning a game engine</t>
+          <t>Bite-sized coding lessons you complete in your browser with instant feedback</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>learn-anything.xyz</t>
+          <t>internet-janitor.itch.io</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>https://learn-anything.xyz</t>
+          <t>https://internet-janitor.itch.io</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="G357" s="4" t="inlineStr">
         <is>
-          <t>Curated learning paths for any topic - community-organized roadmaps instead of random tutorials</t>
+          <t>Tool for making interactive fiction and clicky experiences without learning a game engine</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>n8n.io</t>
+          <t>learn-anything.xyz</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
@@ -14790,17 +14790,17 @@
       </c>
       <c r="E358" s="5" t="inlineStr">
         <is>
-          <t>https://n8n.io</t>
+          <t>https://learn-anything.xyz</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
         <is>
-          <t>Open-source workflow automation that connects apps and automates tasks with visual builder</t>
+          <t>Curated learning paths for any topic - community-organized roadmaps instead of random tutorials</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>topoexport.com</t>
+          <t>n8n.io</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>https://topoexport.com</t>
+          <t>https://n8n.io</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G359" s="4" t="inlineStr">
         <is>
-          <t>Export 3D terrain models from anywhere on Earth for 3D printing or game development</t>
+          <t>Open-source workflow automation that connects apps and automates tasks with visual builder</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>10015 Tools</t>
+          <t>topoexport.com</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Developer Tools</t>
+          <t>Developer &amp; Code Utility</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -14870,22 +14870,22 @@
       </c>
       <c r="E360" s="5" t="inlineStr">
         <is>
-          <t>https://10015.io</t>
+          <t>https://topoexport.com</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Developer Tools</t>
+          <t>Export 3D terrain models from anywhere on Earth for 3D printing or game development</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -14895,12 +14895,12 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>1aauto.com</t>
+          <t>10015 Tools</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>DIY Vehicle Repair Guides</t>
+          <t>Developer Tools</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>https://1aauto.com</t>
+          <t>https://10015.io</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
@@ -14920,12 +14920,12 @@
       </c>
       <c r="G361" s="4" t="inlineStr">
         <is>
-          <t>Free DIY car repair video guides showing step-by-step fixes for common vehicle problems</t>
+          <t>High-utility web tool: Developer Tools</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -14935,12 +14935,12 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>FilePursuit</t>
+          <t>1aauto.com</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>File Search Engine</t>
+          <t>DIY Vehicle Repair Guides</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="E362" s="5" t="inlineStr">
         <is>
-          <t>https://filepursuit.com</t>
+          <t>https://1aauto.com</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
@@ -14960,12 +14960,12 @@
       </c>
       <c r="G362" s="4" t="inlineStr">
         <is>
-          <t>Open file and media search engine indexing millions of web files.</t>
+          <t>Free DIY car repair video guides showing step-by-step fixes for common vehicle problems</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>Flightradar24</t>
+          <t>FilePursuit</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Flight Tracking</t>
+          <t>File Search Engine</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -14990,22 +14990,22 @@
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>https://www.flightradar24.com</t>
+          <t>https://filepursuit.com</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Flight Tracking</t>
+          <t>Open file and media search engine indexing millions of web files.</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -15015,12 +15015,12 @@
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>MrFreeTools</t>
+          <t>Flightradar24</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Free Online Tools</t>
+          <t>Flight Tracking</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -15030,17 +15030,17 @@
       </c>
       <c r="E364" s="5" t="inlineStr">
         <is>
-          <t>https://mrfreetools.com</t>
+          <t>https://www.flightradar24.com</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Free Online Tools</t>
+          <t>High-utility web tool: Flight Tracking</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -15055,12 +15055,12 @@
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>ifixit.com</t>
+          <t>MrFreeTools</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Hardware &amp; Device Repair Guides</t>
+          <t>Free Online Tools</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>https://ifixit.com</t>
+          <t>https://mrfreetools.com</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
@@ -15080,12 +15080,12 @@
       </c>
       <c r="G365" s="4" t="inlineStr">
         <is>
-          <t>Free repair guides for phones laptops and appliances - fix it yourself and save money</t>
+          <t>High-utility web tool: Free Online Tools</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>PI7 Image Tool</t>
+          <t>ifixit.com</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Image Processing Tool</t>
+          <t>Hardware &amp; Device Repair Guides</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="E366" s="5" t="inlineStr">
         <is>
-          <t>https://image.pi7.org</t>
+          <t>https://ifixit.com</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="G366" s="4" t="inlineStr">
         <is>
-          <t>Online image compressor, resizer, and converter tool.</t>
+          <t>Free repair guides for phones laptops and appliances - fix it yourself and save money</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
-          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -15135,12 +15135,12 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>123Apps</t>
+          <t>PI7 Image Tool</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Online Utility Tools</t>
+          <t>Image Processing Tool</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>https://123apps.com</t>
+          <t>https://image.pi7.org</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
@@ -15160,12 +15160,12 @@
       </c>
       <c r="G367" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Online Utility Tools</t>
+          <t>Online image compressor, resizer, and converter tool.</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: ⬇️ Video Downloaders.xlsx</t>
         </is>
       </c>
     </row>
@@ -15175,12 +15175,12 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>archive.ph</t>
+          <t>123Apps</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Permanent Web Archiving Utility</t>
+          <t>Online Utility Tools</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="E368" s="5" t="inlineStr">
         <is>
-          <t>https://archive.ph</t>
+          <t>https://123apps.com</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
@@ -15200,12 +15200,12 @@
       </c>
       <c r="G368" s="4" t="inlineStr">
         <is>
-          <t>Save permanent copies of web pages before they change or disappear forever</t>
+          <t>High-utility web tool: Online Utility Tools</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>autocatalogarchive.com</t>
+          <t>archive.ph</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>https://autocatalogarchive.com</t>
+          <t>https://archive.ph</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="G369" s="4" t="inlineStr">
         <is>
-          <t>Archive of vintage car brochures and catalogs for classic vehicle research and nostalgia</t>
+          <t>Save permanent copies of web pages before they change or disappear forever</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>fakeupdate.net</t>
+          <t>autocatalogarchive.com</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Productivity Tool</t>
+          <t>Permanent Web Archiving Utility</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="E370" s="5" t="inlineStr">
         <is>
-          <t>https://fakeupdate.net</t>
+          <t>https://autocatalogarchive.com</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="G370" s="4" t="inlineStr">
         <is>
-          <t>Fake system update screens perfect for office pranks or looking busy during meetings</t>
+          <t>Archive of vintage car brochures and catalogs for classic vehicle research and nostalgia</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>haveibeenpwned.com</t>
+          <t>fakeupdate.net</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>https://haveibeenpwned.com</t>
+          <t>https://fakeupdate.net</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G371" s="4" t="inlineStr">
         <is>
-          <t>Check if your email or password appeared in data breaches - everyone should use this</t>
+          <t>Fake system update screens perfect for office pranks or looking busy during meetings</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>makemydrivefun.com</t>
+          <t>haveibeenpwned.com</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="E372" s="5" t="inlineStr">
         <is>
-          <t>https://makemydrivefun.com</t>
+          <t>https://haveibeenpwned.com</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="G372" s="4" t="inlineStr">
         <is>
-          <t>Find quirky roadside attractions and interesting detours along your planned driving route</t>
+          <t>Check if your email or password appeared in data breaches - everyone should use this</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>ssemble.com</t>
+          <t>makemydrivefun.com</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
@@ -15390,17 +15390,17 @@
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>https://ssemble.com</t>
+          <t>https://makemydrivefun.com</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
         <is>
-          <t>Browser-based video editor with AI features for creating and editing without downloads</t>
+          <t>Find quirky roadside attractions and interesting detours along your planned driving route</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>stirlingpdf.io</t>
+          <t>ssemble.com</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
@@ -15430,17 +15430,17 @@
       </c>
       <c r="E374" s="5" t="inlineStr">
         <is>
-          <t>https://stirlingpdf.io</t>
+          <t>https://ssemble.com</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
-          <t>Open-source all-in-one PDF manipulation tool you can self-host for privacy</t>
+          <t>Browser-based video editor with AI features for creating and editing without downloads</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>trace.moe</t>
+          <t>stirlingpdf.io</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>https://trace.moe</t>
+          <t>https://stirlingpdf.io</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="G375" s="4" t="inlineStr">
         <is>
-          <t>Reverse image search for anime that identifies the exact scene from any screenshot</t>
+          <t>Open-source all-in-one PDF manipulation tool you can self-host for privacy</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>unpigeon.me</t>
+          <t>trace.moe</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="E376" s="5" t="inlineStr">
         <is>
-          <t>https://unpigeon.me</t>
+          <t>https://trace.moe</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="G376" s="4" t="inlineStr">
         <is>
-          <t>Convert email newsletter subscriptions to RSS feeds to escape inbox clutter</t>
+          <t>Reverse image search for anime that identifies the exact scene from any screenshot</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>versus.com</t>
+          <t>unpigeon.me</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>https://versus.com</t>
+          <t>https://unpigeon.me</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="G377" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side product comparisons with detailed spec breakdowns across phones laptops and more</t>
+          <t>Convert email newsletter subscriptions to RSS feeds to escape inbox clutter</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -15575,12 +15575,12 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>Useful Free Online Tools &amp; Sites</t>
+          <t>versus.com</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Tool Collection (GitHub)</t>
+          <t>Productivity Tool</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="E378" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/J0rgeSerran0/Useful-Free-Online-Tools-and-Sites</t>
+          <t>https://versus.com</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
@@ -15600,12 +15600,12 @@
       </c>
       <c r="G378" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Tool Collection (GitHub)</t>
+          <t>Side-by-side product comparisons with detailed spec breakdowns across phones laptops and more</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>drivenlisten.com</t>
+          <t>Useful Free Online Tools &amp; Sites</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Utility Tool</t>
+          <t>Tool Collection (GitHub)</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>https://drivenlisten.com</t>
+          <t>https://github.com/J0rgeSerran0/Useful-Free-Online-Tools-and-Sites</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
@@ -15640,12 +15640,12 @@
       </c>
       <c r="G379" s="4" t="inlineStr">
         <is>
-          <t>Virtual drives through cities worldwide with real dashcam footage and local radio</t>
+          <t>High-utility web tool: Tool Collection (GitHub)</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>entertrained.app</t>
+          <t>drivenlisten.com</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="E380" s="5" t="inlineStr">
         <is>
-          <t>https://entertrained.app</t>
+          <t>https://drivenlisten.com</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="G380" s="4" t="inlineStr">
         <is>
-          <t>Practice typing by retyping classic books - skill building while reading great literature</t>
+          <t>Virtual drives through cities worldwide with real dashcam footage and local radio</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>freesewing.eu</t>
+          <t>entertrained.app</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>https://freesewing.eu</t>
+          <t>https://entertrained.app</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="G381" s="4" t="inlineStr">
         <is>
-          <t>Generate custom sewing patterns from your exact body measurements - open source and free</t>
+          <t>Practice typing by retyping classic books - skill building while reading great literature</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>mcbroken.com</t>
+          <t>freesewing.eu</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="E382" s="5" t="inlineStr">
         <is>
-          <t>https://mcbroken.com</t>
+          <t>https://freesewing.eu</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="G382" s="4" t="inlineStr">
         <is>
-          <t>Check if the McDonald's ice cream machine near you is working before you drive there</t>
+          <t>Generate custom sewing patterns from your exact body measurements - open source and free</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>myfridgefood.com</t>
+          <t>mcbroken.com</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>https://myfridgefood.com</t>
+          <t>https://mcbroken.com</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="G383" s="4" t="inlineStr">
         <is>
-          <t>Recipe finder that suggests meals based on ingredients you already have at home</t>
+          <t>Check if the McDonald's ice cream machine near you is working before you drive there</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>onelook.com</t>
+          <t>myfridgefood.com</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="E384" s="5" t="inlineStr">
         <is>
-          <t>https://onelook.com</t>
+          <t>https://myfridgefood.com</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="G384" s="4" t="inlineStr">
         <is>
-          <t>Reverse dictionary that finds words when you only know the definition or concept</t>
+          <t>Recipe finder that suggests meals based on ingredients you already have at home</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>pointerpointer.com</t>
+          <t>onelook.com</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>https://pointerpointer.com</t>
+          <t>https://onelook.com</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G385" s="4" t="inlineStr">
         <is>
-          <t>Whimsical website that finds photos of people pointing exactly where your cursor is</t>
+          <t>Reverse dictionary that finds words when you only know the definition or concept</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>roadtrippers.com</t>
+          <t>pointerpointer.com</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
@@ -15910,17 +15910,17 @@
       </c>
       <c r="E386" s="5" t="inlineStr">
         <is>
-          <t>https://roadtrippers.com</t>
+          <t>https://pointerpointer.com</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G386" s="4" t="inlineStr">
         <is>
-          <t>Road trip planning tool with stops attractions and route optimization all in one</t>
+          <t>Whimsical website that finds photos of people pointing exactly where your cursor is</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>wifimap.io</t>
+          <t>roadtrippers.com</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>https://wifimap.io</t>
+          <t>https://roadtrippers.com</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="G387" s="4" t="inlineStr">
         <is>
-          <t>Crowdsourced database of WiFi passwords from cafes airports and public places worldwide</t>
+          <t>Road trip planning tool with stops attractions and route optimization all in one</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -15975,12 +15975,12 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Website Planet Tools</t>
+          <t>wifimap.io</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Web Utilities</t>
+          <t>Utility Tool</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -15990,22 +15990,22 @@
       </c>
       <c r="E388" s="5" t="inlineStr">
         <is>
-          <t>https://www.websiteplanet.com/webtools</t>
+          <t>https://wifimap.io</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Web Utilities</t>
+          <t>Crowdsourced database of WiFi passwords from cafes airports and public places worldwide</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
       </c>
     </row>
@@ -16015,12 +16015,12 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>xTiles</t>
+          <t>Website Planet Tools</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Workspace / Productivity</t>
+          <t>Web Utilities</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -16030,17 +16030,17 @@
       </c>
       <c r="E389" s="5" t="inlineStr">
         <is>
-          <t>https://xtiles.app/workspace/personal</t>
+          <t>https://www.websiteplanet.com/webtools</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>Free + Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
         <is>
-          <t>High-utility web tool: Workspace / Productivity</t>
+          <t>High-utility web tool: Web Utilities</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -16055,37 +16055,37 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>3dtuning.com</t>
+          <t>xTiles</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>3D Virtual Vehicle Customizer</t>
+          <t>Workspace / Productivity</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>🎨 Design &amp; Creator Tools</t>
+          <t>🛠️ Web Utilities &amp; Productivity</t>
         </is>
       </c>
       <c r="E390" s="5" t="inlineStr">
         <is>
-          <t>https://3dtuning.com</t>
+          <t>https://xtiles.app/workspace/personal</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free + Paid</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
         <is>
-          <t>Virtual car customization tool to visualize modifications and dream builds before spending money</t>
+          <t>High-utility web tool: Workspace / Productivity</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Sheet3)</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16095,7 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>carcarekiosk.com</t>
+          <t>3dtuning.com</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
@@ -16110,17 +16110,17 @@
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>https://carcarekiosk.com</t>
+          <t>https://3dtuning.com</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr">
         <is>
-          <t>Vehicle-specific maintenance video tutorials for your exact car make and model</t>
+          <t>Virtual car customization tool to visualize modifications and dream builds before spending money</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>dora.run</t>
+          <t>carcarekiosk.com</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
@@ -16150,17 +16150,17 @@
       </c>
       <c r="E392" s="5" t="inlineStr">
         <is>
-          <t>https://dora.run</t>
+          <t>https://carcarekiosk.com</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
         <is>
-          <t>No-code builder for impressive 3D animated websites without learning WebGL or Three.js</t>
+          <t>Vehicle-specific maintenance video tutorials for your exact car make and model</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>home.by.me</t>
+          <t>dora.run</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="E393" s="5" t="inlineStr">
         <is>
-          <t>https://home.by.me</t>
+          <t>https://dora.run</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="G393" s="4" t="inlineStr">
         <is>
-          <t>3D home design and room planner to visualize renovations before committing to changes</t>
+          <t>No-code builder for impressive 3D animated websites without learning WebGL or Three.js</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>pacdora.com</t>
+          <t>home.by.me</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="E394" s="5" t="inlineStr">
         <is>
-          <t>https://pacdora.com</t>
+          <t>https://home.by.me</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="G394" s="4" t="inlineStr">
         <is>
-          <t>3D packaging mockup generator for product branding with realistic visualization</t>
+          <t>3D home design and room planner to visualize renovations before committing to changes</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>startmycar.com</t>
+          <t>pacdora.com</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
@@ -16270,17 +16270,17 @@
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>https://startmycar.com</t>
+          <t>https://pacdora.com</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
         <is>
-          <t>Car troubleshooting guide that helps diagnose why your car won't start with solutions</t>
+          <t>3D packaging mockup generator for product branding with realistic visualization</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>jitter.video</t>
+          <t>startmycar.com</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Browser-Based Video Editor</t>
+          <t>3D Virtual Vehicle Customizer</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -16310,17 +16310,17 @@
       </c>
       <c r="E396" s="5" t="inlineStr">
         <is>
-          <t>https://jitter.video</t>
+          <t>https://startmycar.com</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
         <is>
-          <t>Browser-based motion graphics editor for designers who don't want to learn After Effects</t>
+          <t>Car troubleshooting guide that helps diagnose why your car won't start with solutions</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>musclewiki.com</t>
+          <t>jitter.video</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
@@ -16350,17 +16350,17 @@
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>https://musclewiki.com</t>
+          <t>https://jitter.video</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
         <is>
-          <t>Interactive muscle map showing exercises for every body part with video demonstrations</t>
+          <t>Browser-based motion graphics editor for designers who don't want to learn After Effects</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>whitescreen.online</t>
+          <t>musclewiki.com</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="E398" s="5" t="inlineStr">
         <is>
-          <t>https://whitescreen.online</t>
+          <t>https://musclewiki.com</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="G398" s="4" t="inlineStr">
         <is>
-          <t>Full-screen color display for testing monitors lighting video calls or cleaning screens</t>
+          <t>Interactive muscle map showing exercises for every body part with video demonstrations</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>clicktheredbutton.com</t>
+          <t>whitescreen.online</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Creative Design Platform</t>
+          <t>Browser-Based Video Editor</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>https://clicktheredbutton.com</t>
+          <t>https://whitescreen.online</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="G399" s="4" t="inlineStr">
         <is>
-          <t>Random weird website discovery tool - click and find something unexpected on the internet</t>
+          <t>Full-screen color display for testing monitors lighting video calls or cleaning screens</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>dreamforth.com</t>
+          <t>clicktheredbutton.com</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="E400" s="5" t="inlineStr">
         <is>
-          <t>https://dreamforth.com</t>
+          <t>https://clicktheredbutton.com</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="G400" s="4" t="inlineStr">
         <is>
-          <t>Dream interpretation dictionary to explore what your vivid or recurring dreams might mean</t>
+          <t>Random weird website discovery tool - click and find something unexpected on the internet</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>fragrantica.com</t>
+          <t>dreamforth.com</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>https://fragrantica.com</t>
+          <t>https://dreamforth.com</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G401" s="4" t="inlineStr">
         <is>
-          <t>Comprehensive perfume database with detailed notes and community reviews before you buy</t>
+          <t>Dream interpretation dictionary to explore what your vivid or recurring dreams might mean</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>music-map.com</t>
+          <t>fragrantica.com</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="E402" s="5" t="inlineStr">
         <is>
-          <t>https://music-map.com</t>
+          <t>https://fragrantica.com</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="G402" s="4" t="inlineStr">
         <is>
-          <t>Discover similar artists visualized as a spatial map - type any band and explore</t>
+          <t>Comprehensive perfume database with detailed notes and community reviews before you buy</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>nullfake.com</t>
+          <t>music-map.com</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>https://nullfake.com</t>
+          <t>https://music-map.com</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="G403" s="4" t="inlineStr">
         <is>
-          <t>Detect fake Amazon reviews and see adjusted ratings based only on authentic reviews</t>
+          <t>Discover similar artists visualized as a spatial map - type any band and explore</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>supercook.com</t>
+          <t>nullfake.com</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="E404" s="5" t="inlineStr">
         <is>
-          <t>https://supercook.com</t>
+          <t>https://nullfake.com</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G404" s="4" t="inlineStr">
         <is>
-          <t>Recipe search engine that finds dishes you can make with ingredients you already have</t>
+          <t>Detect fake Amazon reviews and see adjusted ratings based only on authentic reviews</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -16655,12 +16655,12 @@
       </c>
       <c r="B405" s="3" t="inlineStr">
         <is>
-          <t>flourish.studio</t>
+          <t>supercook.com</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Design Design Platform</t>
+          <t>Creative Design Platform</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -16670,17 +16670,17 @@
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>https://flourish.studio</t>
+          <t>https://supercook.com</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G405" s="4" t="inlineStr">
         <is>
-          <t>Create beautiful interactive data visualizations and charts without knowing how to code</t>
+          <t>Recipe search engine that finds dishes you can make with ingredients you already have</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>framer.com</t>
+          <t>flourish.studio</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="E406" s="5" t="inlineStr">
         <is>
-          <t>https://framer.com</t>
+          <t>https://flourish.studio</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G406" s="4" t="inlineStr">
         <is>
-          <t>No-code website builder with pixel-perfect control for designers who want professional results</t>
+          <t>Create beautiful interactive data visualizations and charts without knowing how to code</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>planyourroom.com</t>
+          <t>framer.com</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
@@ -16750,17 +16750,17 @@
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>https://planyourroom.com</t>
+          <t>https://framer.com</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G407" s="4" t="inlineStr">
         <is>
-          <t>Drag-and-drop room layout planner to test furniture arrangements before buying or moving</t>
+          <t>No-code website builder with pixel-perfect control for designers who want professional results</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>pngimg.com</t>
+          <t>planyourroom.com</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="E408" s="5" t="inlineStr">
         <is>
-          <t>https://pngimg.com</t>
+          <t>https://planyourroom.com</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="G408" s="4" t="inlineStr">
         <is>
-          <t>Free database of PNG images with transparent backgrounds ready for design projects</t>
+          <t>Drag-and-drop room layout planner to test furniture arrangements before buying or moving</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>reactbits.dev</t>
+          <t>pngimg.com</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>https://reactbits.dev</t>
+          <t>https://pngimg.com</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="G409" s="4" t="inlineStr">
         <is>
-          <t>Collection of animated React components ready to copy and paste into your projects</t>
+          <t>Free database of PNG images with transparent backgrounds ready for design projects</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>squoosh.app</t>
+          <t>reactbits.dev</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="E410" s="5" t="inlineStr">
         <is>
-          <t>https://squoosh.app</t>
+          <t>https://reactbits.dev</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="G410" s="4" t="inlineStr">
         <is>
-          <t>Google's image compression tool with side-by-side comparison to optimize file sizes</t>
+          <t>Collection of animated React components ready to copy and paste into your projects</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>sweezy-cursors.com</t>
+          <t>squoosh.app</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>https://sweezy-cursors.com</t>
+          <t>https://squoosh.app</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="G411" s="4" t="inlineStr">
         <is>
-          <t>Custom animated browser cursors with hundreds of themed and animated styles to choose</t>
+          <t>Google's image compression tool with side-by-side comparison to optimize file sizes</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>tailornova.com</t>
+          <t>sweezy-cursors.com</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
@@ -16950,17 +16950,17 @@
       </c>
       <c r="E412" s="5" t="inlineStr">
         <is>
-          <t>https://tailornova.com</t>
+          <t>https://sweezy-cursors.com</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G412" s="4" t="inlineStr">
         <is>
-          <t>Generate custom sewing patterns made-to-measure from your exact body measurements</t>
+          <t>Custom animated browser cursors with hundreds of themed and animated styles to choose</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>thetruesize.com</t>
+          <t>tailornova.com</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
@@ -16990,17 +16990,17 @@
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>https://thetruesize.com</t>
+          <t>https://tailornova.com</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G413" s="4" t="inlineStr">
         <is>
-          <t>Interactive map showing true size of countries by correcting Mercator projection distortions</t>
+          <t>Generate custom sewing patterns made-to-measure from your exact body measurements</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>typefaceanimator.com</t>
+          <t>thetruesize.com</t>
         </is>
       </c>
       <c r="C414" s="4" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="E414" s="5" t="inlineStr">
         <is>
-          <t>https://typefaceanimator.com</t>
+          <t>https://thetruesize.com</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="G414" s="4" t="inlineStr">
         <is>
-          <t>Browser tool for creating animated typeface transitions and kinetic typography effects</t>
+          <t>Interactive map showing true size of countries by correcting Mercator projection distortions</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>uiball.com</t>
+          <t>typefaceanimator.com</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>https://uiball.com</t>
+          <t>https://typefaceanimator.com</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="G415" s="4" t="inlineStr">
         <is>
-          <t>Free collection of beautiful loading spinners and UI loaders for modern web projects</t>
+          <t>Browser tool for creating animated typeface transitions and kinetic typography effects</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -17095,12 +17095,12 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>animejs.com</t>
+          <t>uiball.com</t>
         </is>
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>JavaScript Web Animation Engine</t>
+          <t>Design Design Platform</t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="E416" s="5" t="inlineStr">
         <is>
-          <t>https://animejs.com</t>
+          <t>https://uiball.com</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="G416" s="4" t="inlineStr">
         <is>
-          <t>Lightweight JavaScript animation library for smooth web animations without heavy dependencies</t>
+          <t>Free collection of beautiful loading spinners and UI loaders for modern web projects</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -17135,7 +17135,7 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>paperanimator.com</t>
+          <t>animejs.com</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
@@ -17150,17 +17150,17 @@
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>https://paperanimator.com</t>
+          <t>https://animejs.com</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G417" s="4" t="inlineStr">
         <is>
-          <t>Turn hand-drawn character sketches into animations with simple drag-and-drop rigging</t>
+          <t>Lightweight JavaScript animation library for smooth web animations without heavy dependencies</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -17175,12 +17175,12 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>hyperpost.studio</t>
+          <t>paperanimator.com</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Social Media Template Booster</t>
+          <t>JavaScript Web Animation Engine</t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="E418" s="5" t="inlineStr">
         <is>
-          <t>https://hyperpost.studio</t>
+          <t>https://paperanimator.com</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="G418" s="4" t="inlineStr">
         <is>
-          <t>Social media template booster packs</t>
+          <t>Turn hand-drawn character sketches into animations with simple drag-and-drop rigging</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>thetoymaker.com</t>
+          <t>hyperpost.studio</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
@@ -17230,17 +17230,17 @@
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>https://thetoymaker.com</t>
+          <t>https://hyperpost.studio</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G419" s="4" t="inlineStr">
         <is>
-          <t>Printable paper toy templates you can cut fold and glue into whimsical 3D figures</t>
+          <t>Social media template booster packs</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -17255,22 +17255,22 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>beforeiplay.com</t>
+          <t>thetoymaker.com</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Browser Game &amp; Interactive Entertainment</t>
+          <t>Social Media Template Booster</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>🎮 Gaming &amp; Entertainment</t>
+          <t>🎨 Design &amp; Creator Tools</t>
         </is>
       </c>
       <c r="E420" s="5" t="inlineStr">
         <is>
-          <t>https://beforeiplay.com</t>
+          <t>https://thetoymaker.com</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="G420" s="4" t="inlineStr">
         <is>
-          <t>Spoiler-free tips and advice to read before starting any new video game</t>
+          <t>Printable paper toy templates you can cut fold and glue into whimsical 3D figures</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>builditapp.com</t>
+          <t>beforeiplay.com</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
@@ -17310,17 +17310,17 @@
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>https://builditapp.com</t>
+          <t>https://beforeiplay.com</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G421" s="4" t="inlineStr">
         <is>
-          <t>Step-by-step Minecraft building guides with layer-by-layer instructions for impressive structures</t>
+          <t>Spoiler-free tips and advice to read before starting any new video game</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>chunkbase.com</t>
+          <t>builditapp.com</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
@@ -17350,17 +17350,17 @@
       </c>
       <c r="E422" s="5" t="inlineStr">
         <is>
-          <t>https://chunkbase.com</t>
+          <t>https://builditapp.com</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G422" s="4" t="inlineStr">
         <is>
-          <t>Find Minecraft structures and biomes by entering your world seed before exploring</t>
+          <t>Step-by-step Minecraft building guides with layer-by-layer instructions for impressive structures</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>lostgamer.io</t>
+          <t>chunkbase.com</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>https://lostgamer.io</t>
+          <t>https://chunkbase.com</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="G423" s="4" t="inlineStr">
         <is>
-          <t>GeoGuessr but for video games - guess your location from in-game screenshots</t>
+          <t>Find Minecraft structures and biomes by entering your world seed before exploring</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -17415,7 +17415,7 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>moewalls.com</t>
+          <t>lostgamer.io</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="E424" s="5" t="inlineStr">
         <is>
-          <t>https://moewalls.com</t>
+          <t>https://lostgamer.io</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="G424" s="4" t="inlineStr">
         <is>
-          <t>Animated wallpapers and live desktop backgrounds for Windows with huge variety</t>
+          <t>GeoGuessr but for video games - guess your location from in-game screenshots</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>slowroads.io</t>
+          <t>moewalls.com</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>https://slowroads.io</t>
+          <t>https://moewalls.com</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="G425" s="4" t="inlineStr">
         <is>
-          <t>Relaxing endless driving game with procedurally generated roads through beautiful landscapes</t>
+          <t>Animated wallpapers and live desktop backgrounds for Windows with huge variety</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>systemrequirementslab.com</t>
+          <t>slowroads.io</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="E426" s="5" t="inlineStr">
         <is>
-          <t>https://systemrequirementslab.com</t>
+          <t>https://slowroads.io</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="G426" s="4" t="inlineStr">
         <is>
-          <t>Check if your PC can run a game by scanning your specs against requirements</t>
+          <t>Relaxing endless driving game with procedurally generated roads through beautiful landscapes</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -17535,12 +17535,12 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>azgaar.github.io</t>
+          <t>systemrequirementslab.com</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Interactive Fantasy Map Generator</t>
+          <t>Browser Game &amp; Interactive Entertainment</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>https://azgaar.github.io</t>
+          <t>https://systemrequirementslab.com</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G427" s="4" t="inlineStr">
         <is>
-          <t>Procedural fantasy map generator for D&amp;D campaigns and worldbuilding projects</t>
+          <t>Check if your PC can run a game by scanning your specs against requirements</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>mapgenie.io</t>
+          <t>azgaar.github.io</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
@@ -17590,17 +17590,17 @@
       </c>
       <c r="E428" s="5" t="inlineStr">
         <is>
-          <t>https://mapgenie.io</t>
+          <t>https://azgaar.github.io</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G428" s="4" t="inlineStr">
         <is>
-          <t>Interactive game maps with collectible tracking for completionists who want 100% in games</t>
+          <t>Procedural fantasy map generator for D&amp;D campaigns and worldbuilding projects</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>watabou.github.io</t>
+          <t>mapgenie.io</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
@@ -17630,17 +17630,17 @@
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>https://watabou.github.io</t>
+          <t>https://mapgenie.io</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="G429" s="4" t="inlineStr">
         <is>
-          <t>Collection of procedural generators for dungeon maps medieval cities and fantasy worlds</t>
+          <t>Interactive game maps with collectible tracking for completionists who want 100% in games</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -17655,35 +17655,75 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
+          <t>watabou.github.io</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="inlineStr">
+        <is>
+          <t>Interactive Fantasy Map Generator</t>
+        </is>
+      </c>
+      <c r="D430" s="4" t="inlineStr">
+        <is>
+          <t>🎮 Gaming &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="E430" s="5" t="inlineStr">
+        <is>
+          <t>https://watabou.github.io</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>Collection of procedural generators for dungeon maps medieval cities and fantasy worlds</t>
+        </is>
+      </c>
+      <c r="H430" s="4" t="inlineStr">
+        <is>
+          <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
           <t>airconsole.com</t>
         </is>
       </c>
-      <c r="C430" s="4" t="inlineStr">
+      <c r="C431" s="4" t="inlineStr">
         <is>
           <t>Phone-Controller Multiplayer Games</t>
         </is>
       </c>
-      <c r="D430" s="4" t="inlineStr">
+      <c r="D431" s="4" t="inlineStr">
         <is>
           <t>🎮 Gaming &amp; Entertainment</t>
         </is>
       </c>
-      <c r="E430" s="5" t="inlineStr">
+      <c r="E431" s="5" t="inlineStr">
         <is>
           <t>https://airconsole.com</t>
         </is>
       </c>
-      <c r="F430" s="2" t="inlineStr">
+      <c r="F431" s="2" t="inlineStr">
         <is>
           <t>Freemium</t>
         </is>
       </c>
-      <c r="G430" s="4" t="inlineStr">
+      <c r="G431" s="4" t="inlineStr">
         <is>
           <t>Multiplayer party games using phones as controllers - no console or downloads needed</t>
         </is>
       </c>
-      <c r="H430" s="4" t="inlineStr">
+      <c r="H431" s="4" t="inlineStr">
         <is>
           <t>Excel: 🌐 Powerful Websites.xlsx (Websites-BH)</t>
         </is>
@@ -18120,6 +18160,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E428" r:id="rId427"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E429" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E431" r:id="rId430"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21778,7 +21819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30653,7 +30694,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>HTML Visuals</t>
+          <t>Explorer.globe.engineer</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -30668,7 +30709,7 @@
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>https://www.htmlvisuals.com</t>
+          <t>https://explorer.globe.engineer</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -30678,7 +30719,7 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: HTML Visuals (Web Development Resource)</t>
+          <t>High-utility developer platform: Explorer.globe.engineer (Web Development Resource)</t>
         </is>
       </c>
     </row>
@@ -30688,7 +30729,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>HTML.com</t>
+          <t>HTML Visuals</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -30703,7 +30744,7 @@
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>https://html.com</t>
+          <t>https://www.htmlvisuals.com</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -30713,7 +30754,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: HTML.com (Web Development Resource)</t>
+          <t>High-utility developer platform: HTML Visuals (Web Development Resource)</t>
         </is>
       </c>
     </row>
@@ -30723,7 +30764,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>HTML5 Cheat Sheet</t>
+          <t>HTML.com</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -30738,7 +30779,7 @@
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>https://www.geeksforgeeks.org/html5-cheat-sheet</t>
+          <t>https://html.com</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -30748,7 +30789,7 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: HTML5 Cheat Sheet (Web Development Resource)</t>
+          <t>High-utility developer platform: HTML.com (Web Development Resource)</t>
         </is>
       </c>
     </row>
@@ -30758,7 +30799,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>LearnWeb3</t>
+          <t>HTML5 Cheat Sheet</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -30773,7 +30814,7 @@
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>https://learnweb3.io</t>
+          <t>https://www.geeksforgeeks.org/html5-cheat-sheet</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -30783,7 +30824,7 @@
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: LearnWeb3 (Web Development Resource)</t>
+          <t>High-utility developer platform: HTML5 Cheat Sheet (Web Development Resource)</t>
         </is>
       </c>
     </row>
@@ -30793,7 +30834,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>W3Schools</t>
+          <t>LearnWeb3</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -30808,7 +30849,7 @@
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>https://www.w3schools.com</t>
+          <t>https://learnweb3.io</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -30818,7 +30859,7 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>High-utility developer platform: W3Schools (Web Development Resource)</t>
+          <t>High-utility developer platform: LearnWeb3 (Web Development Resource)</t>
         </is>
       </c>
     </row>
@@ -30828,22 +30869,22 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Academind</t>
+          <t>W3Schools</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>📺 Programming Creators &amp; Channels (YouTube &amp; Social)</t>
+          <t>📚 Developer Reference, Roadmaps &amp; Cheat Sheets</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>YouTube Coding Channel</t>
+          <t>Web Development Resource</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@academind</t>
+          <t>https://www.w3schools.com</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -30853,7 +30894,7 @@
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>Deep-dive technical tutorials on React, Angular, Vue, Node.js, and cloud tech.</t>
+          <t>High-utility developer platform: W3Schools (Web Development Resource)</t>
         </is>
       </c>
     </row>
@@ -30878,7 +30919,7 @@
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Academind</t>
+          <t>https://www.youtube.com/@academind</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -30888,7 +30929,7 @@
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>Developer platform: Academind (YouTube Coding Channel)</t>
+          <t>Deep-dive technical tutorials on React, Angular, Vue, Node.js, and cloud tech.</t>
         </is>
       </c>
     </row>
@@ -30898,7 +30939,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Anuj Bhaiya</t>
+          <t>Academind</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -30913,7 +30954,7 @@
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AnujBhaiya</t>
+          <t>https://www.youtube.com/@Academind</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -30923,7 +30964,7 @@
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>Data structures, algorithms, system design, and software engineering placement prep.</t>
+          <t>Developer platform: Academind (YouTube Coding Channel)</t>
         </is>
       </c>
     </row>
@@ -30933,7 +30974,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Apni Kaksha</t>
+          <t>Anuj Bhaiya</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
@@ -30948,7 +30989,7 @@
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ApniKaksha</t>
+          <t>https://www.youtube.com/@AnujBhaiya</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -30958,7 +30999,7 @@
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>Free quality coding education, college roadmap, and placement interview guidance.</t>
+          <t>Data structures, algorithms, system design, and software engineering placement prep.</t>
         </is>
       </c>
     </row>
@@ -30968,7 +31009,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Bhagwan Singh Vishwakarma</t>
+          <t>Apni Kaksha</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -30983,7 +31024,7 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@bhagwansinghvishwakarma</t>
+          <t>https://www.youtube.com/@ApniKaksha</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -30993,7 +31034,7 @@
       </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>Computer science, programming, and technical academic tutorials.</t>
+          <t>Free quality coding education, college roadmap, and placement interview guidance.</t>
         </is>
       </c>
     </row>
@@ -31003,7 +31044,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Clever Programmer</t>
+          <t>Bhagwan Singh Vishwakarma</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -31018,7 +31059,7 @@
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CleverProgrammer</t>
+          <t>https://www.youtube.com/@bhagwansinghvishwakarma</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -31028,7 +31069,7 @@
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>Full-stack web development clone builds with JavaScript, React, and Python.</t>
+          <t>Computer science, programming, and technical academic tutorials.</t>
         </is>
       </c>
     </row>
@@ -31038,7 +31079,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>CodeWithHarry</t>
+          <t>Clever Programmer</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -31053,7 +31094,7 @@
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CodeWithHarry</t>
+          <t>https://www.youtube.com/@CleverProgrammer</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -31063,7 +31104,7 @@
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>Top Indian programming channel teaching Python, Web Dev, C, C++, and Java in Hindi.</t>
+          <t>Full-stack web development clone builds with JavaScript, React, and Python.</t>
         </is>
       </c>
     </row>
@@ -31073,7 +31114,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Derek Banas</t>
+          <t>CodeWithHarry</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
@@ -31088,7 +31129,7 @@
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@derekbanas</t>
+          <t>https://www.youtube.com/@CodeWithHarry</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -31098,7 +31139,7 @@
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>Learn complex programming languages and frameworks in single comprehensive videos.</t>
+          <t>Top Indian programming channel teaching Python, Web Dev, C, C++, and Java in Hindi.</t>
         </is>
       </c>
     </row>
@@ -31108,7 +31149,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>freeCodeCamp.org</t>
+          <t>Derek Banas</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -31123,7 +31164,7 @@
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@freecodecamp</t>
+          <t>https://www.youtube.com/@derekbanas</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
@@ -31133,7 +31174,7 @@
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
-          <t>Thousands of hours of free coding courses from industry professionals.</t>
+          <t>Learn complex programming languages and frameworks in single comprehensive videos.</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31184,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Gate Smashers</t>
+          <t>freeCodeCamp.org</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
@@ -31158,7 +31199,7 @@
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GateSmashers</t>
+          <t>https://www.youtube.com/@freecodecamp</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
@@ -31168,7 +31209,7 @@
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>Operating systems, DBMS, computer networks, and GATE computer science lectures.</t>
+          <t>Thousands of hours of free coding courses from industry professionals.</t>
         </is>
       </c>
     </row>
@@ -31178,7 +31219,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Jenny's Lectures CS IT</t>
+          <t>Gate Smashers</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -31193,7 +31234,7 @@
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@JennyslecturesCSIT</t>
+          <t>https://www.youtube.com/@GateSmashers</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -31203,7 +31244,7 @@
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
-          <t>Engineering CS/IT subjects, algorithms, data structures, and theory of computation.</t>
+          <t>Operating systems, DBMS, computer networks, and GATE computer science lectures.</t>
         </is>
       </c>
     </row>
@@ -31213,7 +31254,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>LearnCode.academy</t>
+          <t>Jenny's Lectures CS IT</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
@@ -31228,7 +31269,7 @@
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@learncodeacademy</t>
+          <t>https://www.youtube.com/@JennyslecturesCSIT</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -31238,7 +31279,7 @@
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>Web development tutorials, responsive design, JavaScript, React, and DevOps.</t>
+          <t>Engineering CS/IT subjects, algorithms, data structures, and theory of computation.</t>
         </is>
       </c>
     </row>
@@ -31248,7 +31289,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>mycodeschool</t>
+          <t>LearnCode.academy</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -31263,7 +31304,7 @@
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@mycodeschool</t>
+          <t>https://www.youtube.com/@learncodeacademy</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -31273,7 +31314,7 @@
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>Classic, world-renowned lessons on data structures, pointers, and memory management.</t>
+          <t>Web development tutorials, responsive design, JavaScript, React, and DevOps.</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31324,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>MySirG.com</t>
+          <t>mycodeschool</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
@@ -31298,7 +31339,7 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MySirG</t>
+          <t>https://www.youtube.com/@mycodeschool</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -31308,7 +31349,7 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>Premier Hindi channel for C, C++, Python, Data Structures, and programming fundamentals.</t>
+          <t>Classic, world-renowned lessons on data structures, pointers, and memory management.</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31359,7 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Programming Hub</t>
+          <t>MySirG.com</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -31333,7 +31374,7 @@
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProgrammingHub</t>
+          <t>https://www.youtube.com/@MySirG</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
@@ -31343,7 +31384,7 @@
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>Accessible tech tutorials covering AI, app development, and programming languages.</t>
+          <t>Premier Hindi channel for C, C++, Python, Data Structures, and programming fundamentals.</t>
         </is>
       </c>
     </row>
@@ -31353,7 +31394,7 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Programming with Mosh</t>
+          <t>Programming Hub</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
@@ -31368,7 +31409,7 @@
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@programmingwithmosh</t>
+          <t>https://www.youtube.com/@ProgrammingHub</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -31378,7 +31419,7 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>Clear, concise tutorials on Python, JavaScript, React, C#, and SQL.</t>
+          <t>Accessible tech tutorials covering AI, app development, and programming languages.</t>
         </is>
       </c>
     </row>
@@ -31403,7 +31444,7 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProgrammingwithMosh</t>
+          <t>https://www.youtube.com/@programmingwithmosh</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -31413,7 +31454,7 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>Developer platform: Programming with Mosh (YouTube Coding Channel)</t>
+          <t>Clear, concise tutorials on Python, JavaScript, React, C#, and SQL.</t>
         </is>
       </c>
     </row>
@@ -31423,7 +31464,7 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>ProgrammingKnowledge</t>
+          <t>Programming with Mosh</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
@@ -31438,7 +31479,7 @@
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProgrammingKnowledge</t>
+          <t>https://www.youtube.com/@ProgrammingwithMosh</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -31448,7 +31489,7 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>Step-by-step programming tutorials on Android, Java, Python, and Linux.</t>
+          <t>Developer platform: Programming with Mosh (YouTube Coding Channel)</t>
         </is>
       </c>
     </row>
@@ -31458,7 +31499,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>SoloLearn</t>
+          <t>ProgrammingKnowledge</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -31473,7 +31514,7 @@
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SoloLearn</t>
+          <t>https://www.youtube.com/@ProgrammingKnowledge</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
@@ -31483,7 +31524,7 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>Bite-sized mobile-first coding lessons and language deep-dives.</t>
+          <t>Step-by-step programming tutorials on Android, Java, Python, and Linux.</t>
         </is>
       </c>
     </row>
@@ -31493,7 +31534,7 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>SortedCoding</t>
+          <t>SoloLearn</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
@@ -31508,7 +31549,7 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SortedCoding</t>
+          <t>https://www.youtube.com/@SoloLearn</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -31518,7 +31559,7 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>Frontend tricks, CSS animations, JavaScript projects, and coding shorts.</t>
+          <t>Bite-sized mobile-first coding lessons and language deep-dives.</t>
         </is>
       </c>
     </row>
@@ -31543,7 +31584,7 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>https://youtube.com/@sortedcoding?si=OViA9rO2lCUgosxT</t>
+          <t>https://www.youtube.com/@SortedCoding</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -31553,7 +31594,7 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>Developer platform: SortedCoding (YouTube Coding Channel)</t>
+          <t>Frontend tricks, CSS animations, JavaScript projects, and coding shorts.</t>
         </is>
       </c>
     </row>
@@ -31563,7 +31604,7 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Telusko</t>
+          <t>SortedCoding</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
@@ -31578,7 +31619,7 @@
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Telusko</t>
+          <t>https://youtube.com/@sortedcoding?si=OViA9rO2lCUgosxT</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -31588,7 +31629,7 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>Java, Python, Blockchain, Docker, and full-stack web development tutorials.</t>
+          <t>Developer platform: SortedCoding (YouTube Coding Channel)</t>
         </is>
       </c>
     </row>
@@ -31598,7 +31639,7 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>thenewboston</t>
+          <t>Telusko</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -31613,7 +31654,7 @@
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@thenewboston</t>
+          <t>https://www.youtube.com/@Telusko</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
@@ -31623,7 +31664,7 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>Pioneering computer science, web dev, and blockchain video tutorials.</t>
+          <t>Java, Python, Blockchain, Docker, and full-stack web development tutorials.</t>
         </is>
       </c>
     </row>
@@ -31633,30 +31674,65 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
+          <t>thenewboston</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>📺 Programming Creators &amp; Channels (YouTube &amp; Social)</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>YouTube Coding Channel</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@thenewboston</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>Pioneering computer science, web dev, and blockchain video tutorials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
           <t>Traversy Media</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr">
+      <c r="C283" s="4" t="inlineStr">
         <is>
           <t>📺 Programming Creators &amp; Channels (YouTube &amp; Social)</t>
         </is>
       </c>
-      <c r="D282" s="4" t="inlineStr">
+      <c r="D283" s="4" t="inlineStr">
         <is>
           <t>YouTube Coding Channel</t>
         </is>
       </c>
-      <c r="E282" s="5" t="inlineStr">
+      <c r="E283" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@TraversyMedia</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="G282" s="4" t="inlineStr">
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
         <is>
           <t>Practical web development tutorials, crash courses, and project builds.</t>
         </is>
@@ -31945,6 +32021,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId279"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId282"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
